--- a/tame_output/ON/bt/strategyON_20240415.xlsx
+++ b/tame_output/ON/bt/strategyON_20240415.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>53.3%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.1%</t>
+          <t>-79.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>119.0%</t>
+          <t>118.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>138.8%</t>
+          <t>138.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-722.5%</t>
+          <t>-709.2%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.8%</t>
+          <t>-57.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.1%</t>
+          <t>-74.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.7%</t>
+          <t>98.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>749.5%</t>
+          <t>755.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-550.3%</t>
+          <t>-550.5%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-283.6%</t>
+          <t>-278.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.2%</t>
+          <t>-44.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-128.6%</t>
+          <t>177.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.1%</t>
+          <t>-29.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>71.8%</t>
+          <t>71.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.5%</t>
+          <t>-38.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-22.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-251.4%</t>
+          <t>-248.7%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>49.1%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1471,17 +1471,17 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.2%</t>
+          <t>-33.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-157.6%</t>
+          <t>-156.0%</t>
         </is>
       </c>
     </row>
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.02467440532598</v>
+        <v>-11.89189801645925</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.651165739622107</v>
+        <v>-1.598055184075416</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.579146780620141</v>
+        <v>-3.552669758134569</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.011572378449949</v>
+        <v>1.027458591941292</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.25670332506224</v>
+        <v>-12.12392693619551</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.741283578887498</v>
+        <v>-1.688173023340806</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.641159477808564</v>
+        <v>-3.614682455322992</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9770584887660094</v>
+        <v>0.9929447022573528</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.20468781109343</v>
+        <v>-12.0719114222267</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.716487037613572</v>
+        <v>-1.66337648206688</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.641159477808564</v>
+        <v>-3.614682455322992</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.9810488244524103</v>
+        <v>0.9969350379437536</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.34635965281755</v>
+        <v>-12.21358326395082</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.774631001201961</v>
+        <v>-1.72152044565527</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.641159477808564</v>
+        <v>-3.614682455322992</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.9795735975536686</v>
+        <v>0.9954598110450119</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.44526639327683</v>
+        <v>-12.3124900044101</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.799140287220799</v>
+        <v>-1.746029731674108</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.740066218267839</v>
+        <v>-3.713589195782267</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.9352829634429756</v>
+        <v>0.9511691769343189</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.24611428603973</v>
+        <v>-12.113337897173</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.732530577972642</v>
+        <v>-1.679420022425951</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.574743692318026</v>
+        <v>-3.548266669832454</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.021425345366181</v>
+        <v>1.037311558857524</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.02026913332032</v>
+        <v>-11.88749274445359</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.632613443848669</v>
+        <v>-1.579502888301978</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.532817016730863</v>
+        <v>-3.50633999424529</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.056160423754688</v>
+        <v>1.072046637246031</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.73399432099762</v>
+        <v>-11.60121793213089</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.516964374363532</v>
+        <v>-1.463853818816841</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.532817016730863</v>
+        <v>-3.50633999424529</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.057299568310746</v>
+        <v>1.07318578180209</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.78688960904191</v>
+        <v>-11.65411322017518</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.535488715419139</v>
+        <v>-1.482378159872448</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.527861670642416</v>
+        <v>-3.501384648156844</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.062906550125922</v>
+        <v>1.078792763617265</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.50298087811316</v>
+        <v>-11.37020448924643</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.416191518809003</v>
+        <v>-1.363080963262312</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.527861670642416</v>
+        <v>-3.501384648156844</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.068640254364558</v>
+        <v>1.084526467855901</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.25599362792021</v>
+        <v>-11.12321723905348</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.327133881125688</v>
+        <v>-1.274023325578996</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.280874420449464</v>
+        <v>-3.254397397963892</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.207095342086464</v>
+        <v>1.222981555577808</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.99215676071614</v>
+        <v>-10.85938037184941</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.231482615556967</v>
+        <v>-1.178372060010277</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.280874420449464</v>
+        <v>-3.254397397963892</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.197211860773557</v>
+        <v>1.2130980742649</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.72491495984774</v>
+        <v>-10.59213857098101</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.126420455708982</v>
+        <v>-1.073309900162291</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.280874420449464</v>
+        <v>-3.254397397963892</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.195377300274183</v>
+        <v>1.211263513765526</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.44910579644725</v>
+        <v>-10.31632940758053</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.016397105322249</v>
+        <v>-0.9632865497755581</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.191855112170731</v>
+        <v>-3.165378089685158</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.248488570267962</v>
+        <v>1.264374783759306</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.4251522554713</v>
+        <v>-10.29237586660457</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.006147182786372</v>
+        <v>-0.9530366272396811</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.167901571194773</v>
+        <v>-3.141424548709201</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.26352920099903</v>
+        <v>1.279415414490374</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.1610923171485</v>
+        <v>-10.02831592828177</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9137835236190055</v>
+        <v>-0.8606729680723149</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.903841632871977</v>
+        <v>-2.877364610386405</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.408704847830956</v>
+        <v>1.424591061322299</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.454012693643662</v>
+        <v>-9.321236304776935</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6337387078773711</v>
+        <v>-0.5806281523306804</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.903841632871977</v>
+        <v>-2.877364610386405</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.405917814170655</v>
+        <v>1.421804027661998</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.413828395277472</v>
+        <v>-9.281052006410745</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6173213646430535</v>
+        <v>-0.5642108090963629</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.863657334505787</v>
+        <v>-2.837180312020214</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.430372017078211</v>
+        <v>1.446258230569554</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.333758599739667</v>
+        <v>-9.20098221087294</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5859266252071751</v>
+        <v>-0.532816069660484</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.783587538967982</v>
+        <v>-2.75711051648241</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.47778071562165</v>
+        <v>1.493666929112994</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.100277377510068</v>
+        <v>-8.967500988643341</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.4846097074774827</v>
+        <v>-0.431499151930792</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.550106316738384</v>
+        <v>-2.523629294252812</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.625793877797262</v>
+        <v>1.641680091288605</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.920568847366194</v>
+        <v>-8.787792458499467</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4156185057328927</v>
+        <v>-0.3625079501862016</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.492934812575688</v>
+        <v>-2.466457790090116</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.65720456998192</v>
+        <v>1.673090783473263</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.788293373735307</v>
+        <v>-8.65551698486858</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3673408295335108</v>
+        <v>-0.3142302739868197</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.360659338944802</v>
+        <v>-2.334182316459229</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.731937340907479</v>
+        <v>1.747823554398822</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.597693699062154</v>
+        <v>-8.464917310195426</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2882858989766124</v>
+        <v>-0.2351753434299217</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.170059664271649</v>
+        <v>-2.143582641786077</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.849112206399007</v>
+        <v>1.864998419890351</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.348693900378573</v>
+        <v>-8.215917511511845</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1757796382795216</v>
+        <v>-0.1226690827328305</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.170059664271649</v>
+        <v>-2.143582641786077</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.862018547622666</v>
+        <v>1.877904761114009</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.454283890151677</v>
+        <v>-8.32150750128495</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.3459915637879818</v>
+        <v>-0.2928810082412912</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.275649654044754</v>
+        <v>-2.249172631559181</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.670688624159584</v>
+        <v>1.686574837650928</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.473018792270274</v>
+        <v>-8.340242403403547</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3049411827583342</v>
+        <v>-0.2518306272116435</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.275649654044754</v>
+        <v>-2.249172631559181</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.719232966036671</v>
+        <v>1.735119179528014</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.196280617599461</v>
+        <v>-8.063504228732734</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1908669009040147</v>
+        <v>-0.1377563453573236</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.093832992934828</v>
+        <v>-2.067355970449255</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.831701974688621</v>
+        <v>1.847588188179965</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.069388211164391</v>
+        <v>-7.936611822297664</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1488239245834646</v>
+        <v>-0.09571336903677397</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.966940586499758</v>
+        <v>-1.940463564014185</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.899123432296185</v>
+        <v>1.915009645787528</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.0258398043937</v>
+        <v>-7.893063415526973</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1383651739702811</v>
+        <v>-0.08525461842359094</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.966940586499758</v>
+        <v>-1.940463564014185</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.892162820201092</v>
+        <v>1.908049033692435</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.783691410939841</v>
+        <v>-7.650915022073115</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.02704346220759479</v>
+        <v>0.0260670933390954</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.966940586499758</v>
+        <v>-1.940463564014185</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.906625174582235</v>
+        <v>1.922511388073578</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.720462039171493</v>
+        <v>-7.587685650304767</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.007219593041060346</v>
+        <v>0.04589096250562985</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.966940586499758</v>
+        <v>-1.940463564014185</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.90115729504143</v>
+        <v>1.917043508532773</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.533974346794487</v>
+        <v>-7.401197957927761</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.06487357792031867</v>
+        <v>0.1179841334670093</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.780452894122752</v>
+        <v>-1.753975871637179</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.01054800447821</v>
+        <v>2.026434217969554</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.512825147891044</v>
+        <v>-7.380048759024318</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.08103423571902191</v>
+        <v>0.1341447912657121</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.759303695219308</v>
+        <v>-1.732826672733736</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.030938502057602</v>
+        <v>2.046824715548945</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.269059705907599</v>
+        <v>-7.136283317040873</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.17432112085945</v>
+        <v>0.2274316764061406</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.759303695219308</v>
+        <v>-1.732826672733736</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.026719210404653</v>
+        <v>2.042605423895996</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.005031638714339</v>
+        <v>-6.872255249847614</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2820566616567701</v>
+        <v>0.3351672172034603</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.557438296403355</v>
+        <v>-1.530961273917782</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.149962763614241</v>
+        <v>2.165848977105584</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.755181244765264</v>
+        <v>-6.622404855898539</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3747388942201022</v>
+        <v>0.4278494497667924</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.557438296403355</v>
+        <v>-1.530961273917782</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.142704838597943</v>
+        <v>2.158591052089286</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.451613755761286</v>
+        <v>-6.31883736689456</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4997650133423424</v>
+        <v>0.5528755688890326</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.557438296403355</v>
+        <v>-1.530961273917782</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.146303962118592</v>
+        <v>2.162190175609935</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.378133846909272</v>
+        <v>-6.245357458042546</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5424844829377018</v>
+        <v>0.595595038484392</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.48395838755134</v>
+        <v>-1.457481365065768</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.203719413484354</v>
+        <v>2.219605626975698</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.153100847240449</v>
+        <v>-6.020324458373723</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6315181604215279</v>
+        <v>0.6846287159682181</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.258925387882517</v>
+        <v>-1.232448365396945</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.337759690901945</v>
+        <v>2.353645904393288</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.938466469604042</v>
+        <v>-5.805690080737317</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7220667125304079</v>
+        <v>0.7751772680770981</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.04429101024611</v>
+        <v>-1.017813987760538</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.471235118538106</v>
+        <v>2.487121332029449</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.67186611262969</v>
+        <v>-5.539089723762965</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8099011141039445</v>
+        <v>0.8630116696506347</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.04429101024611</v>
+        <v>-1.017813987760538</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.452429377321902</v>
+        <v>2.468315590813245</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.43143561582483</v>
+        <v>-5.298659226958105</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9078163894507658</v>
+        <v>0.960926944997456</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8038605134412502</v>
+        <v>-0.7773834909556778</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.598430752029695</v>
+        <v>2.614316965521039</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.188644808175384</v>
+        <v>-5.055868419308659</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.008862026345364</v>
+        <v>1.061972581892054</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8038605134412502</v>
+        <v>-0.7773834909556778</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.602360065864516</v>
+        <v>2.618246279355859</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.949039716568295</v>
+        <v>-4.81626332770157</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.10538264690554</v>
+        <v>1.15849320245223</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7368125657727557</v>
+        <v>-0.7103355432871833</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.643267418382952</v>
+        <v>2.659153631874295</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.706384128145132</v>
+        <v>-4.573607739278406</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.199442953494799</v>
+        <v>1.252553509041489</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7368125657727557</v>
+        <v>-0.7103355432871833</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.640265489602946</v>
+        <v>2.656151703094289</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.486363330108121</v>
+        <v>-4.353586941241396</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.289030309720217</v>
+        <v>1.342140865266907</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5955927207047754</v>
+        <v>-0.569115698219203</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.726576433654348</v>
+        <v>2.742462647145691</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.287114700203312</v>
+        <v>-4.154338311336587</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.384623944483964</v>
+        <v>1.437734500030654</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5955927207047754</v>
+        <v>-0.569115698219203</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.742470616456171</v>
+        <v>2.758356829947515</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>3.100972093319338</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.127599596683942</v>
+        <v>-3.994823207817217</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.449575830332014</v>
+        <v>1.502686385878704</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4360776171854055</v>
+        <v>-0.4096005946998331</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.839325523008095</v>
+        <v>2.855211736499438</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>3.111060195880778</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.982927451584205</v>
+        <v>-3.85015106271748</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.517532790933349</v>
+        <v>1.570643346480039</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2914054720856681</v>
+        <v>-0.2649284496000957</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.936216912629377</v>
+        <v>2.952103126120721</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>3.0263998879675</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.965157992653249</v>
+        <v>-3.832381603786524</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.439980266592453</v>
+        <v>1.493090822139143</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2736360131547125</v>
+        <v>-0.2471589906691402</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.862218280074672</v>
+        <v>2.878104493566016</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.535742800194638</v>
+        <v>3.813958462684757</v>
       </c>
       <c r="C1934" t="n">
         <v>3.048800381290066</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.887761612824652</v>
+        <v>-3.888970440536049</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.493339311846458</v>
+        <v>1.492855780761899</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2736360131547125</v>
+        <v>-0.2471589906691402</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.884618773397238</v>
+        <v>2.900504986888582</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240415.xlsx
+++ b/tame_output/ON/bt/strategyON_20240415.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.0%</t>
+          <t>-78.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118.6%</t>
+          <t>118.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.7%</t>
+          <t>97.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.7%</t>
+          <t>-74.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.4%</t>
+          <t>98.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>755.3%</t>
+          <t>755.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-550.5%</t>
+          <t>-536.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-226.9%</t>
+          <t>-221.2%</t>
         </is>
       </c>
     </row>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757922</v>
+        <v>3.293490533757923</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.813958462684757</v>
+        <v>3.813958462684758</v>
       </c>
       <c r="C1934" t="n">
         <v>3.048800381290066</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.888970440536049</v>
+        <v>-3.745582106007515</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.492855780761899</v>
+        <v>1.550211114573312</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.2471589906691402</v>

--- a/tame_output/ON/bt/strategyON_20240415.xlsx
+++ b/tame_output/ON/bt/strategyON_20240415.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-13.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>13.0%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.4%</t>
+          <t>-79.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>138.2%</t>
+          <t>138.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.8%</t>
+          <t>97.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-709.2%</t>
+          <t>-722.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.3%</t>
+          <t>-57.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.1%</t>
+          <t>-76.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.5%</t>
+          <t>98.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>755.7%</t>
+          <t>746.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-536.1%</t>
+          <t>-562.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-278.3%</t>
+          <t>-283.6%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.8%</t>
+          <t>-45.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-21.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>177.9%</t>
+          <t>-39.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-221.2%</t>
+          <t>-231.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.7%</t>
+          <t>-28.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>71.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.3%</t>
+          <t>-38.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-22.7%</t>
+          <t>-22.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.6%</t>
+          <t>-155.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-248.7%</t>
+          <t>-241.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,32 +1466,32 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.1%</t>
+          <t>-33.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-156.0%</t>
+          <t>-151.7%</t>
         </is>
       </c>
     </row>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757923</v>
+        <v>3.293490533757922</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296837</v>
+        <v>3.299918119296838</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153007</v>
+        <v>3.258791981153008</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537426</v>
+        <v>3.271168579537427</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.49371243886058</v>
+        <v>3.493712438860579</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.89189801645925</v>
+        <v>-12.02467440532598</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.598055184075416</v>
+        <v>-1.651165739622107</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.552669758134569</v>
+        <v>-3.579146780620141</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.027458591941292</v>
+        <v>1.011572378449949</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767394</v>
+        <v>3.492098065767393</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.12392693619551</v>
+        <v>-12.25670332506224</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.688173023340806</v>
+        <v>-1.741283578887498</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.614682455322992</v>
+        <v>-3.641159477808564</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9929447022573528</v>
+        <v>0.9770584887660094</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792539</v>
+        <v>3.573670449792538</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.0719114222267</v>
+        <v>-12.20468781109343</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.66337648206688</v>
+        <v>-1.716487037613572</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.614682455322992</v>
+        <v>-3.641159477808564</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.9969350379437536</v>
+        <v>0.9810488244524103</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628917</v>
+        <v>3.600034689628916</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.21358326395082</v>
+        <v>-12.34635965281755</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.72152044565527</v>
+        <v>-1.774631001201961</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.614682455322992</v>
+        <v>-3.641159477808564</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.9954598110450119</v>
+        <v>0.9795735975536686</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410715</v>
+        <v>3.691568158410714</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.3124900044101</v>
+        <v>-12.44526639327683</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.746029731674108</v>
+        <v>-1.799140287220799</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.713589195782267</v>
+        <v>-3.740066218267839</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.9511691769343189</v>
+        <v>0.9352829634429756</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240574</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.113337897173</v>
+        <v>-12.24611428603973</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.679420022425951</v>
+        <v>-1.732530577972642</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.548266669832454</v>
+        <v>-3.574743692318026</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.037311558857524</v>
+        <v>1.021425345366181</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.88749274445359</v>
+        <v>-12.02026913332032</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.579502888301978</v>
+        <v>-1.632613443848669</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.50633999424529</v>
+        <v>-3.532817016730863</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.072046637246031</v>
+        <v>1.056160423754688</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282098</v>
+        <v>3.684840248282097</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.60121793213089</v>
+        <v>-11.73399432099762</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.463853818816841</v>
+        <v>-1.516964374363532</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.50633999424529</v>
+        <v>-3.532817016730863</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.07318578180209</v>
+        <v>1.057299568310746</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.710931958116212</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.65411322017518</v>
+        <v>-11.78688960904191</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.482378159872448</v>
+        <v>-1.535488715419139</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.501384648156844</v>
+        <v>-3.527861670642416</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.078792763617265</v>
+        <v>1.062906550125922</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081564</v>
+        <v>3.768948099081563</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.37020448924643</v>
+        <v>-11.50298087811316</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.363080963262312</v>
+        <v>-1.416191518809003</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.501384648156844</v>
+        <v>-3.527861670642416</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.084526467855901</v>
+        <v>1.068640254364558</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425325</v>
+        <v>3.728574354425324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.12321723905348</v>
+        <v>-11.25599362792021</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.274023325578996</v>
+        <v>-1.327133881125688</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.254397397963892</v>
+        <v>-3.280874420449464</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.222981555577808</v>
+        <v>1.207095342086464</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702409</v>
+        <v>3.747699084702408</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.85938037184941</v>
+        <v>-10.99215676071614</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.178372060010277</v>
+        <v>-1.231482615556967</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.254397397963892</v>
+        <v>-3.280874420449464</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.2130980742649</v>
+        <v>1.197211860773557</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906225</v>
+        <v>3.766313503906224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.59213857098101</v>
+        <v>-10.72491495984774</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.073309900162291</v>
+        <v>-1.126420455708982</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.254397397963892</v>
+        <v>-3.280874420449464</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.211263513765526</v>
+        <v>1.195377300274183</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781946</v>
+        <v>3.784680945781945</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.31632940758053</v>
+        <v>-10.44910579644725</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.9632865497755581</v>
+        <v>-1.016397105322249</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.165378089685158</v>
+        <v>-3.191855112170731</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.264374783759306</v>
+        <v>1.248488570267962</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.29237586660457</v>
+        <v>-10.4251522554713</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.9530366272396811</v>
+        <v>-1.006147182786372</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.141424548709201</v>
+        <v>-3.167901571194773</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.279415414490374</v>
+        <v>1.26352920099903</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487771</v>
+        <v>3.78930753648777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.02831592828177</v>
+        <v>-10.1610923171485</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.8606729680723149</v>
+        <v>-0.9137835236190055</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.877364610386405</v>
+        <v>-2.903841632871977</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.424591061322299</v>
+        <v>1.408704847830956</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309724</v>
+        <v>3.833249172309722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.321236304776935</v>
+        <v>-9.454012693643662</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.5806281523306804</v>
+        <v>-0.6337387078773711</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.877364610386405</v>
+        <v>-2.903841632871977</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.421804027661998</v>
+        <v>1.405917814170655</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858728</v>
+        <v>3.839370871858726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.281052006410745</v>
+        <v>-9.413828395277472</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.5642108090963629</v>
+        <v>-0.6173213646430535</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.837180312020214</v>
+        <v>-2.863657334505787</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.446258230569554</v>
+        <v>1.430372017078211</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096473</v>
+        <v>3.856158176096471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.20098221087294</v>
+        <v>-9.333758599739667</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.532816069660484</v>
+        <v>-0.5859266252071751</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.75711051648241</v>
+        <v>-2.783587538967982</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.493666929112994</v>
+        <v>1.47778071562165</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761807</v>
+        <v>3.787326853761805</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.967500988643341</v>
+        <v>-9.100277377510068</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.431499151930792</v>
+        <v>-0.4846097074774827</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.523629294252812</v>
+        <v>-2.550106316738384</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.641680091288605</v>
+        <v>1.625793877797262</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255783</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.787792458499467</v>
+        <v>-8.920568847366194</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3625079501862016</v>
+        <v>-0.4156185057328927</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.466457790090116</v>
+        <v>-2.492934812575688</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.673090783473263</v>
+        <v>1.65720456998192</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860425</v>
+        <v>3.763178672860423</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.65551698486858</v>
+        <v>-8.788293373735307</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3142302739868197</v>
+        <v>-0.3673408295335108</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.334182316459229</v>
+        <v>-2.360659338944802</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.747823554398822</v>
+        <v>1.731937340907479</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.78471521857595</v>
+        <v>3.784715218575948</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.464917310195426</v>
+        <v>-8.597693699062154</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2351753434299217</v>
+        <v>-0.2882858989766124</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.143582641786077</v>
+        <v>-2.170059664271649</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.864998419890351</v>
+        <v>1.849112206399007</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430985</v>
+        <v>3.753878996430982</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.215917511511845</v>
+        <v>-8.459644583246723</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1226690827328305</v>
+        <v>-0.2201599114267814</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.143582641786077</v>
+        <v>-2.170059664271649</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.877904761114009</v>
+        <v>1.862018547622666</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077643</v>
+        <v>3.69292828007764</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.32150750128495</v>
+        <v>-8.565234573019827</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2928810082412912</v>
+        <v>-0.390371836935242</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.249172631559181</v>
+        <v>-2.275649654044754</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.686574837650928</v>
+        <v>1.670688624159584</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457898</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.340242403403547</v>
+        <v>-8.583969475138424</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2518306272116435</v>
+        <v>-0.3493214559055944</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.249172631559181</v>
+        <v>-2.275649654044754</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.735119179528014</v>
+        <v>1.719232966036671</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.063504228732734</v>
+        <v>-8.307231300467611</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1377563453573236</v>
+        <v>-0.2352471740512745</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.067355970449255</v>
+        <v>-2.093832992934828</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.847588188179965</v>
+        <v>1.831701974688621</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879199</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.936611822297664</v>
+        <v>-8.180338894032541</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.09571336903677397</v>
+        <v>-0.1932041977307248</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.940463564014185</v>
+        <v>-1.966940586499758</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.915009645787528</v>
+        <v>1.899123432296185</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568103</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.893063415526973</v>
+        <v>-8.13679048726185</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.08525461842359094</v>
+        <v>-0.1827454471175414</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.940463564014185</v>
+        <v>-1.966940586499758</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.908049033692435</v>
+        <v>1.892162820201092</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963414</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.650915022073115</v>
+        <v>-7.894642093807992</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.0260670933390954</v>
+        <v>-0.07142373535485502</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.940463564014185</v>
+        <v>-1.966940586499758</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.922511388073578</v>
+        <v>1.906625174582235</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192814</v>
+        <v>3.82854791119281</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.587685650304767</v>
+        <v>-7.831412722039643</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.04589096250562985</v>
+        <v>-0.05159986618832058</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.940463564014185</v>
+        <v>-1.966940586499758</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.917043508532773</v>
+        <v>1.90115729504143</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262044</v>
+        <v>3.82804935326204</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.401197957927761</v>
+        <v>-7.644925029662637</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1179841334670093</v>
+        <v>0.02049330477305844</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.753975871637179</v>
+        <v>-1.780452894122752</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.026434217969554</v>
+        <v>2.01054800447821</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389906</v>
+        <v>3.812450103389902</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.380048759024318</v>
+        <v>-7.525789606029331</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1341447912657121</v>
+        <v>0.07584845246370664</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.732826672733736</v>
+        <v>-1.661317470489445</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.046824715548945</v>
+        <v>2.08973023689552</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788091</v>
+        <v>3.748324832788088</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.136283317040873</v>
+        <v>-7.282024164045887</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2274316764061406</v>
+        <v>0.1691353376041351</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.732826672733736</v>
+        <v>-1.661317470489445</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.042605423895996</v>
+        <v>2.085510945242571</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527523</v>
+        <v>3.82430765752752</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.872255249847614</v>
+        <v>-7.017996096852627</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3351672172034603</v>
+        <v>0.2768708784014549</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.530961273917782</v>
+        <v>-1.459452071673492</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.165848977105584</v>
+        <v>2.208754498452159</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749182</v>
+        <v>3.826351398749178</v>
       </c>
       <c r="C1919" t="n">
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.622404855898539</v>
+        <v>-6.768145702903553</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4278494497667924</v>
+        <v>0.3695531109647869</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.530961273917782</v>
+        <v>-1.459452071673492</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.158591052089286</v>
+        <v>2.201496573435861</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481495</v>
+        <v>3.835954411481492</v>
       </c>
       <c r="C1920" t="n">
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.31883736689456</v>
+        <v>-6.464578213899574</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5528755688890326</v>
+        <v>0.4945792300870271</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.530961273917782</v>
+        <v>-1.459452071673492</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.162190175609935</v>
+        <v>2.205095696956509</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862984</v>
+        <v>3.780930335862981</v>
       </c>
       <c r="C1921" t="n">
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.245357458042546</v>
+        <v>-6.39109830504756</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.595595038484392</v>
+        <v>0.5372986996823865</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.457481365065768</v>
+        <v>-1.385972162821477</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.219605626975698</v>
+        <v>2.262511148322272</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102779</v>
+        <v>3.773761647102775</v>
       </c>
       <c r="C1922" t="n">
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.020324458373723</v>
+        <v>-6.166065305378737</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6846287159682181</v>
+        <v>0.6263323771662126</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.232448365396945</v>
+        <v>-1.160939163152654</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.353645904393288</v>
+        <v>2.396551425739863</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353072</v>
+        <v>3.764614304353068</v>
       </c>
       <c r="C1923" t="n">
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.805690080737317</v>
+        <v>-5.95143092774233</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7751772680770981</v>
+        <v>0.7168809292750926</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.017813987760538</v>
+        <v>-0.9463047855162476</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.487121332029449</v>
+        <v>2.530026853376024</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881119554478</v>
+        <v>3.798811195544777</v>
       </c>
       <c r="C1924" t="n">
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.539089723762965</v>
+        <v>-5.684830570767978</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8630116696506347</v>
+        <v>0.8047153308486292</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.017813987760538</v>
+        <v>-0.9463047855162476</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.468315590813245</v>
+        <v>2.51122111215982</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712292</v>
+        <v>3.797691308712288</v>
       </c>
       <c r="C1925" t="n">
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.298659226958105</v>
+        <v>-5.444400073963118</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.960926944997456</v>
+        <v>0.9026306061954505</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7773834909556778</v>
+        <v>-0.7058742887113874</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.614316965521039</v>
+        <v>2.657222486867613</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837682</v>
+        <v>3.821589933837679</v>
       </c>
       <c r="C1926" t="n">
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.055868419308659</v>
+        <v>-5.201609266313673</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.061972581892054</v>
+        <v>1.003676243090049</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7773834909556778</v>
+        <v>-0.7058742887113874</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.618246279355859</v>
+        <v>2.661151800702433</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349964</v>
+        <v>3.82232342234996</v>
       </c>
       <c r="C1927" t="n">
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.81626332770157</v>
+        <v>-4.962004174706584</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.15849320245223</v>
+        <v>1.100196863650225</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7103355432871833</v>
+        <v>-0.6388263410428928</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.659153631874295</v>
+        <v>2.70205915322087</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972337</v>
+        <v>3.848613050972333</v>
       </c>
       <c r="C1928" t="n">
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.573607739278406</v>
+        <v>-4.71934858628342</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.252553509041489</v>
+        <v>1.194257170239484</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7103355432871833</v>
+        <v>-0.6388263410428928</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.656151703094289</v>
+        <v>2.699057224440863</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145937</v>
+        <v>3.818665376145933</v>
       </c>
       <c r="C1929" t="n">
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.353586941241396</v>
+        <v>-4.49932778824641</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.342140865266907</v>
+        <v>1.283844526464902</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.569115698219203</v>
+        <v>-0.4976064959749126</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.742462647145691</v>
+        <v>2.785368168492266</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009949</v>
+        <v>3.843270952009945</v>
       </c>
       <c r="C1930" t="n">
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.154338311336587</v>
+        <v>-4.3000791583416</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.437734500030654</v>
+        <v>1.379438161228649</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.569115698219203</v>
+        <v>-0.4976064959749126</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.758356829947515</v>
+        <v>2.801262351294089</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966256</v>
+        <v>3.845043810966253</v>
       </c>
       <c r="C1931" t="n">
         <v>3.100972093319338</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.994823207817217</v>
+        <v>-4.140564054822231</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.502686385878704</v>
+        <v>1.444390047076699</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4096005946998331</v>
+        <v>-0.3380913924555426</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.855211736499438</v>
+        <v>2.898117257846013</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046992</v>
+        <v>3.791269976046989</v>
       </c>
       <c r="C1932" t="n">
         <v>3.111060195880778</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.85015106271748</v>
+        <v>-3.995891909722493</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.570643346480039</v>
+        <v>1.512347007678033</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2649284496000957</v>
+        <v>-0.1934192473558052</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.952103126120721</v>
+        <v>2.995008647467295</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412099</v>
+        <v>3.735835647412095</v>
       </c>
       <c r="C1933" t="n">
         <v>3.0263998879675</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.832381603786524</v>
+        <v>-3.978122450791538</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.493090822139143</v>
+        <v>1.434794483337137</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2471589906691402</v>
+        <v>-0.1756497884248497</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.878104493566016</v>
+        <v>2.92101001491259</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.813958462684758</v>
+        <v>3.411271410615435</v>
       </c>
       <c r="C1934" t="n">
         <v>3.048800381290066</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.745582106007515</v>
+        <v>-4.011991508545627</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.550211114573312</v>
+        <v>1.443647353558068</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2471589906691402</v>
+        <v>-0.1756497884248497</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.900504986888582</v>
+        <v>2.943410508235156</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240415.xlsx
+++ b/tame_output/ON/bt/strategyON_20240415.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>53.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>75.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -824,17 +824,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>10.4%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.5%</t>
+          <t>-78.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118.7%</t>
+          <t>118.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>138.7%</t>
+          <t>138.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>97.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-722.5%</t>
+          <t>-709.2%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.8%</t>
+          <t>-57.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.1%</t>
+          <t>-74.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.6%</t>
+          <t>98.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>746.5%</t>
+          <t>754.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-562.8%</t>
+          <t>-536.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,22 +1102,22 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-283.6%</t>
+          <t>-278.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.2%</t>
+          <t>-44.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-21.2%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-39.3%</t>
+          <t>177.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-231.9%</t>
+          <t>-221.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-28.9%</t>
+          <t>-29.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>71.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,17 +1260,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.5%</t>
+          <t>-38.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-22.8%</t>
+          <t>-22.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.9%</t>
+          <t>-155.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-241.6%</t>
+          <t>-248.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,27 +1466,27 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.2%</t>
+          <t>-33.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-151.7%</t>
+          <t>-124.7%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1934"/>
+  <dimension ref="A1:G1935"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757922</v>
+        <v>3.293490533757923</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296838</v>
+        <v>3.299918119296837</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153008</v>
+        <v>3.258791981153007</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537427</v>
+        <v>3.271168579537426</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860579</v>
+        <v>3.49371243886058</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.02467440532598</v>
+        <v>-11.89189801645925</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.651165739622107</v>
+        <v>-1.598055184075416</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.579146780620141</v>
+        <v>-3.552669758134569</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.011572378449949</v>
+        <v>1.027458591941292</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767393</v>
+        <v>3.492098065767394</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.25670332506224</v>
+        <v>-12.12392693619551</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.741283578887498</v>
+        <v>-1.688173023340806</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.641159477808564</v>
+        <v>-3.614682455322992</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9770584887660094</v>
+        <v>0.9929447022573528</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792538</v>
+        <v>3.573670449792539</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.20468781109343</v>
+        <v>-12.0719114222267</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.716487037613572</v>
+        <v>-1.66337648206688</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.641159477808564</v>
+        <v>-3.614682455322992</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.9810488244524103</v>
+        <v>0.9969350379437536</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628916</v>
+        <v>3.600034689628917</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.34635965281755</v>
+        <v>-12.21358326395082</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.774631001201961</v>
+        <v>-1.72152044565527</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.641159477808564</v>
+        <v>-3.614682455322992</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.9795735975536686</v>
+        <v>0.9954598110450119</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410714</v>
+        <v>3.691568158410715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.44526639327683</v>
+        <v>-12.3124900044101</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.799140287220799</v>
+        <v>-1.746029731674108</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.740066218267839</v>
+        <v>-3.713589195782267</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.9352829634429756</v>
+        <v>0.9511691769343189</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240574</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.24611428603973</v>
+        <v>-12.113337897173</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.732530577972642</v>
+        <v>-1.679420022425951</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.574743692318026</v>
+        <v>-3.548266669832454</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.021425345366181</v>
+        <v>1.037311558857524</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.02026913332032</v>
+        <v>-11.88749274445359</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.632613443848669</v>
+        <v>-1.579502888301978</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.532817016730863</v>
+        <v>-3.50633999424529</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.056160423754688</v>
+        <v>1.072046637246031</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282097</v>
+        <v>3.684840248282098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.73399432099762</v>
+        <v>-11.60121793213089</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.516964374363532</v>
+        <v>-1.463853818816841</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.532817016730863</v>
+        <v>-3.50633999424529</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.057299568310746</v>
+        <v>1.07318578180209</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116212</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.78688960904191</v>
+        <v>-11.65411322017518</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.535488715419139</v>
+        <v>-1.482378159872448</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.527861670642416</v>
+        <v>-3.501384648156844</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.062906550125922</v>
+        <v>1.078792763617265</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081563</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.50298087811316</v>
+        <v>-11.37020448924643</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.416191518809003</v>
+        <v>-1.363080963262312</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.527861670642416</v>
+        <v>-3.501384648156844</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.068640254364558</v>
+        <v>1.084526467855901</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425324</v>
+        <v>3.728574354425325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.25599362792021</v>
+        <v>-11.12321723905348</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.327133881125688</v>
+        <v>-1.274023325578996</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.280874420449464</v>
+        <v>-3.254397397963892</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.207095342086464</v>
+        <v>1.222981555577808</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702408</v>
+        <v>3.747699084702409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.99215676071614</v>
+        <v>-10.85938037184941</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.231482615556967</v>
+        <v>-1.178372060010277</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.280874420449464</v>
+        <v>-3.254397397963892</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.197211860773557</v>
+        <v>1.2130980742649</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906224</v>
+        <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.72491495984774</v>
+        <v>-10.59213857098101</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.126420455708982</v>
+        <v>-1.073309900162291</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.280874420449464</v>
+        <v>-3.254397397963892</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.195377300274183</v>
+        <v>1.211263513765526</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781945</v>
+        <v>3.784680945781946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.44910579644725</v>
+        <v>-10.31632940758053</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.016397105322249</v>
+        <v>-0.9632865497755581</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.191855112170731</v>
+        <v>-3.165378089685158</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.248488570267962</v>
+        <v>1.264374783759306</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.4251522554713</v>
+        <v>-10.29237586660457</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.006147182786372</v>
+        <v>-0.9530366272396811</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.167901571194773</v>
+        <v>-3.141424548709201</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.26352920099903</v>
+        <v>1.279415414490374</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78930753648777</v>
+        <v>3.789307536487771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.1610923171485</v>
+        <v>-10.02831592828177</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9137835236190055</v>
+        <v>-0.8606729680723149</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.903841632871977</v>
+        <v>-2.877364610386405</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.408704847830956</v>
+        <v>1.424591061322299</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309722</v>
+        <v>3.833249172309724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.454012693643662</v>
+        <v>-9.321236304776935</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6337387078773711</v>
+        <v>-0.5806281523306804</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.903841632871977</v>
+        <v>-2.877364610386405</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.405917814170655</v>
+        <v>1.421804027661998</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858726</v>
+        <v>3.839370871858728</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.413828395277472</v>
+        <v>-9.281052006410745</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6173213646430535</v>
+        <v>-0.5642108090963629</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.863657334505787</v>
+        <v>-2.837180312020214</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.430372017078211</v>
+        <v>1.446258230569554</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096471</v>
+        <v>3.856158176096473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.333758599739667</v>
+        <v>-9.20098221087294</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5859266252071751</v>
+        <v>-0.532816069660484</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.783587538967982</v>
+        <v>-2.75711051648241</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.47778071562165</v>
+        <v>1.493666929112994</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761805</v>
+        <v>3.787326853761807</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.100277377510068</v>
+        <v>-8.967500988643341</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.4846097074774827</v>
+        <v>-0.431499151930792</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.550106316738384</v>
+        <v>-2.523629294252812</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.625793877797262</v>
+        <v>1.641680091288605</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255783</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.920568847366194</v>
+        <v>-8.787792458499467</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4156185057328927</v>
+        <v>-0.3625079501862016</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.492934812575688</v>
+        <v>-2.466457790090116</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.65720456998192</v>
+        <v>1.673090783473263</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860423</v>
+        <v>3.763178672860425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.788293373735307</v>
+        <v>-8.65551698486858</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3673408295335108</v>
+        <v>-0.3142302739868197</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.360659338944802</v>
+        <v>-2.334182316459229</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.731937340907479</v>
+        <v>1.747823554398822</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575948</v>
+        <v>3.78471521857595</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.597693699062154</v>
+        <v>-8.464917310195426</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2882858989766124</v>
+        <v>-0.2351753434299217</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.170059664271649</v>
+        <v>-2.143582641786077</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.849112206399007</v>
+        <v>1.864998419890351</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430982</v>
+        <v>3.753878996430985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.459644583246723</v>
+        <v>-8.215917511511845</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2201599114267814</v>
+        <v>-0.1226690827328305</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.170059664271649</v>
+        <v>-2.143582641786077</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.862018547622666</v>
+        <v>1.877904761114009</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.69292828007764</v>
+        <v>3.692928280077643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.565234573019827</v>
+        <v>-8.32150750128495</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.390371836935242</v>
+        <v>-0.2928810082412912</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.275649654044754</v>
+        <v>-2.249172631559181</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.670688624159584</v>
+        <v>1.686574837650928</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457898</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.583969475138424</v>
+        <v>-8.340242403403547</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3493214559055944</v>
+        <v>-0.2518306272116435</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.275649654044754</v>
+        <v>-2.249172631559181</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.719232966036671</v>
+        <v>1.735119179528014</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.307231300467611</v>
+        <v>-8.063504228732734</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2352471740512745</v>
+        <v>-0.1377563453573236</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.093832992934828</v>
+        <v>-2.067355970449255</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.831701974688621</v>
+        <v>1.847588188179965</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879199</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.180338894032541</v>
+        <v>-7.936611822297664</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1932041977307248</v>
+        <v>-0.09571336903677397</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.966940586499758</v>
+        <v>-1.940463564014185</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.899123432296185</v>
+        <v>1.915009645787528</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568103</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.13679048726185</v>
+        <v>-7.893063415526973</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1827454471175414</v>
+        <v>-0.08525461842359094</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.966940586499758</v>
+        <v>-1.940463564014185</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.892162820201092</v>
+        <v>1.908049033692435</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963414</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.894642093807992</v>
+        <v>-7.650915022073115</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.07142373535485502</v>
+        <v>0.0260670933390954</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.966940586499758</v>
+        <v>-1.940463564014185</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.906625174582235</v>
+        <v>1.922511388073578</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.82854791119281</v>
+        <v>3.828547911192814</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.831412722039643</v>
+        <v>-7.587685650304767</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.05159986618832058</v>
+        <v>0.04589096250562985</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.966940586499758</v>
+        <v>-1.940463564014185</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.90115729504143</v>
+        <v>1.917043508532773</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.82804935326204</v>
+        <v>3.828049353262044</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.644925029662637</v>
+        <v>-7.401197957927761</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.02049330477305844</v>
+        <v>0.1179841334670093</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.780452894122752</v>
+        <v>-1.753975871637179</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.01054800447821</v>
+        <v>2.026434217969554</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389902</v>
+        <v>3.812450103389906</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.525789606029331</v>
+        <v>-7.380048759024318</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.07584845246370664</v>
+        <v>0.1341447912657121</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.661317470489445</v>
+        <v>-1.732826672733736</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.08973023689552</v>
+        <v>2.046824715548945</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788088</v>
+        <v>3.748324832788091</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.282024164045887</v>
+        <v>-7.136283317040873</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1691353376041351</v>
+        <v>0.2274316764061406</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.661317470489445</v>
+        <v>-1.732826672733736</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.085510945242571</v>
+        <v>2.042605423895996</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.82430765752752</v>
+        <v>3.824307657527523</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.017996096852627</v>
+        <v>-6.872255249847614</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2768708784014549</v>
+        <v>0.3351672172034603</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.459452071673492</v>
+        <v>-1.530961273917782</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.208754498452159</v>
+        <v>2.165848977105584</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749178</v>
+        <v>3.826351398749182</v>
       </c>
       <c r="C1919" t="n">
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.768145702903553</v>
+        <v>-6.622404855898539</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3695531109647869</v>
+        <v>0.4278494497667924</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.459452071673492</v>
+        <v>-1.530961273917782</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.201496573435861</v>
+        <v>2.158591052089286</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481492</v>
+        <v>3.835954411481495</v>
       </c>
       <c r="C1920" t="n">
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.464578213899574</v>
+        <v>-6.31883736689456</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4945792300870271</v>
+        <v>0.5528755688890326</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.459452071673492</v>
+        <v>-1.530961273917782</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.205095696956509</v>
+        <v>2.162190175609935</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862981</v>
+        <v>3.780930335862984</v>
       </c>
       <c r="C1921" t="n">
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.39109830504756</v>
+        <v>-6.245357458042546</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5372986996823865</v>
+        <v>0.595595038484392</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.385972162821477</v>
+        <v>-1.457481365065768</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.262511148322272</v>
+        <v>2.219605626975698</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102775</v>
+        <v>3.773761647102779</v>
       </c>
       <c r="C1922" t="n">
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.166065305378737</v>
+        <v>-6.020324458373723</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6263323771662126</v>
+        <v>0.6846287159682181</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.160939163152654</v>
+        <v>-1.232448365396945</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.396551425739863</v>
+        <v>2.353645904393288</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353068</v>
+        <v>3.764614304353072</v>
       </c>
       <c r="C1923" t="n">
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.95143092774233</v>
+        <v>-5.805690080737317</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7168809292750926</v>
+        <v>0.7751772680770981</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.9463047855162476</v>
+        <v>-1.017813987760538</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.530026853376024</v>
+        <v>2.487121332029449</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544777</v>
+        <v>3.79881119554478</v>
       </c>
       <c r="C1924" t="n">
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.684830570767978</v>
+        <v>-5.539089723762965</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8047153308486292</v>
+        <v>0.8630116696506347</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.9463047855162476</v>
+        <v>-1.017813987760538</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.51122111215982</v>
+        <v>2.468315590813245</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712288</v>
+        <v>3.797691308712292</v>
       </c>
       <c r="C1925" t="n">
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.444400073963118</v>
+        <v>-5.298659226958105</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9026306061954505</v>
+        <v>0.960926944997456</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7058742887113874</v>
+        <v>-0.7773834909556778</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.657222486867613</v>
+        <v>2.614316965521039</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837679</v>
+        <v>3.821589933837682</v>
       </c>
       <c r="C1926" t="n">
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.201609266313673</v>
+        <v>-5.055868419308659</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.003676243090049</v>
+        <v>1.061972581892054</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7058742887113874</v>
+        <v>-0.7773834909556778</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.661151800702433</v>
+        <v>2.618246279355859</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232342234996</v>
+        <v>3.822323422349964</v>
       </c>
       <c r="C1927" t="n">
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.962004174706584</v>
+        <v>-4.81626332770157</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.100196863650225</v>
+        <v>1.15849320245223</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.6388263410428928</v>
+        <v>-0.7103355432871833</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.70205915322087</v>
+        <v>2.659153631874295</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972333</v>
+        <v>3.848613050972337</v>
       </c>
       <c r="C1928" t="n">
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.71934858628342</v>
+        <v>-4.573607739278406</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.194257170239484</v>
+        <v>1.252553509041489</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.6388263410428928</v>
+        <v>-0.7103355432871833</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.699057224440863</v>
+        <v>2.656151703094289</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145933</v>
+        <v>3.818665376145937</v>
       </c>
       <c r="C1929" t="n">
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.49932778824641</v>
+        <v>-4.353586941241396</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.283844526464902</v>
+        <v>1.342140865266907</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4976064959749126</v>
+        <v>-0.569115698219203</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.785368168492266</v>
+        <v>2.742462647145691</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009945</v>
+        <v>3.843270952009949</v>
       </c>
       <c r="C1930" t="n">
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.3000791583416</v>
+        <v>-4.154338311336587</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.379438161228649</v>
+        <v>1.437734500030654</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4976064959749126</v>
+        <v>-0.569115698219203</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.801262351294089</v>
+        <v>2.758356829947515</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966253</v>
+        <v>3.845043810966256</v>
       </c>
       <c r="C1931" t="n">
         <v>3.100972093319338</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.140564054822231</v>
+        <v>-3.994823207817217</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.444390047076699</v>
+        <v>1.502686385878704</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3380913924555426</v>
+        <v>-0.4096005946998331</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.898117257846013</v>
+        <v>2.855211736499438</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046989</v>
+        <v>3.791269976046992</v>
       </c>
       <c r="C1932" t="n">
         <v>3.111060195880778</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.995891909722493</v>
+        <v>-3.85015106271748</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.512347007678033</v>
+        <v>1.570643346480039</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1934192473558052</v>
+        <v>-0.2649284496000957</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.995008647467295</v>
+        <v>2.952103126120721</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412095</v>
+        <v>3.735835647412099</v>
       </c>
       <c r="C1933" t="n">
         <v>3.0263998879675</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.978122450791538</v>
+        <v>-3.832381603786524</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.434794483337137</v>
+        <v>1.493090822139143</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1756497884248497</v>
+        <v>-0.2471589906691402</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.92101001491259</v>
+        <v>2.878104493566016</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,45 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.411271410615435</v>
+        <v>3.762643902144509</v>
       </c>
       <c r="C1934" t="n">
         <v>3.048800381290066</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.011991508545627</v>
+        <v>-3.745582106007515</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.443647353558068</v>
+        <v>1.550211114573312</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.1756497884248497</v>
+        <v>-0.2471589906691402</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.943410508235156</v>
+        <v>2.900504986888582</v>
+      </c>
+    </row>
+    <row r="1935">
+      <c r="A1935" s="2" t="n">
+        <v>45397</v>
+      </c>
+      <c r="B1935" t="n">
+        <v>3.812618724905961</v>
+      </c>
+      <c r="C1935" t="n">
+        <v>3.219861282168526</v>
+      </c>
+      <c r="D1935" t="n">
+        <v>-3.745582106007515</v>
+      </c>
+      <c r="E1935" t="n">
+        <v>1.550211114573312</v>
+      </c>
+      <c r="F1935" t="n">
+        <v>-0.2471589906691402</v>
+      </c>
+      <c r="G1935" t="n">
+        <v>3.212925079154894</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240415.xlsx
+++ b/tame_output/ON/bt/strategyON_20240415.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-13.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>12.3%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -819,27 +819,27 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>-19.2%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.4%</t>
+          <t>-80.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118.6%</t>
+          <t>119.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>138.1%</t>
+          <t>139.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.8%</t>
+          <t>97.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-709.2%</t>
+          <t>-722.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.3%</t>
+          <t>-58.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.1%</t>
+          <t>-77.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.4%</t>
+          <t>98.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>754.6%</t>
+          <t>394.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-536.1%</t>
+          <t>-584.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-278.3%</t>
+          <t>-283.6%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.8%</t>
+          <t>-45.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-29.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>177.7%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-221.2%</t>
+          <t>-240.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.7%</t>
+          <t>-30.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>71.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.3%</t>
+          <t>-38.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-22.7%</t>
+          <t>-24.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.4%</t>
+          <t>-155.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-248.7%</t>
+          <t>-251.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,27 +1466,27 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.1%</t>
+          <t>-33.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-124.7%</t>
+          <t>-154.3%</t>
         </is>
       </c>
     </row>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757923</v>
+        <v>3.293490533757922</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43940,10 +43940,10 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.04813908628406116</v>
+        <v>-0.188352630057362</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.145379929737663</v>
+        <v>3.050783243201093</v>
       </c>
       <c r="F1843" t="n">
         <v>1.711409540942887</v>
@@ -43963,10 +43963,10 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.03363281414369051</v>
+        <v>-0.2701245304851137</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.1027538955218</v>
+        <v>3.008157208985231</v>
       </c>
       <c r="F1844" t="n">
         <v>1.738445114349024</v>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.1008419220155682</v>
+        <v>-0.3373336383569914</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.080635569206751</v>
+        <v>2.986038882670182</v>
       </c>
       <c r="F1845" t="n">
         <v>1.738445114349024</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.09685046922037799</v>
+        <v>-0.3333421855618012</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.080056946444068</v>
+        <v>2.985460259907498</v>
       </c>
       <c r="F1846" t="n">
         <v>1.742436567144214</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.514604492767215</v>
+        <v>-0.7510962091086382</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.910882228530396</v>
+        <v>2.816285541993827</v>
       </c>
       <c r="F1847" t="n">
         <v>1.324682543597377</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.7362264263253324</v>
+        <v>-0.9727181426667557</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.822099671706071</v>
+        <v>2.727502985169502</v>
       </c>
       <c r="F1848" t="n">
         <v>1.287156409910008</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.9442304846784096</v>
+        <v>-1.180722201019833</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.743790192918765</v>
+        <v>2.649193506382196</v>
       </c>
       <c r="F1849" t="n">
         <v>1.287156409910008</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.214630447387295</v>
+        <v>-1.451122163728718</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.630711664173199</v>
+        <v>2.53611497763663</v>
       </c>
       <c r="F1850" t="n">
         <v>1.016756447201123</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.553788824975817</v>
+        <v>-1.79028054131724</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.48813261244424</v>
+        <v>2.39353592590767</v>
       </c>
       <c r="F1851" t="n">
         <v>0.6775980696126005</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.881806046703296</v>
+        <v>-2.118297763044719</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.377264013492016</v>
+        <v>2.282667326955447</v>
       </c>
       <c r="F1852" t="n">
         <v>0.3495808478851213</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.375130918238474</v>
+        <v>-2.611622634579897</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.188032815286514</v>
+        <v>2.093436128749944</v>
       </c>
       <c r="F1853" t="n">
         <v>0.2445947336455026</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.867515946262571</v>
+        <v>-3.104007662603994</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.992185196120607</v>
+        <v>1.897588509584037</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.2477902943785941</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.252696337192643</v>
+        <v>-3.489188053534066</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.836655578561441</v>
+        <v>1.742058892024872</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.2477902943785941</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.596379110419306</v>
+        <v>-3.832870826760729</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.700951592725392</v>
+        <v>1.606354906188823</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.3556963464058123</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.954029460657654</v>
+        <v>-4.190521176999077</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.553997511286311</v>
+        <v>1.459400824749741</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.7133466966441604</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.263263563653705</v>
+        <v>-4.499755279995128</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.43207679678815</v>
+        <v>1.337480110251581</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.7133466966441604</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.695069356803493</v>
+        <v>-4.931561073144915</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.245687366995639</v>
+        <v>1.15109068045907</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.8497641930854274</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.021501885671237</v>
+        <v>-5.257993602012659</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.103399130450633</v>
+        <v>1.008802443914063</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.9322324435925755</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.357164532901689</v>
+        <v>-5.593656249243112</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9677146632144167</v>
+        <v>0.8731179766778472</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.9322324435925755</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.720790777802002</v>
+        <v>-5.957282494143425</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8287517254885328</v>
+        <v>0.7341550389519638</v>
       </c>
       <c r="F1862" t="n">
         <v>-1.030454080459701</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.085918160440749</v>
+        <v>-6.322409876782172</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6819552874388655</v>
+        <v>0.5873586009022964</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.326764864758714</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.494506937621427</v>
+        <v>-6.730998653962851</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.5172813205813536</v>
+        <v>0.4226846340447836</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.735353641939392</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.907489421762521</v>
+        <v>-7.143981138103944</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3472737593963764</v>
+        <v>0.2526770728598069</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.735353641939392</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.323881296049518</v>
+        <v>-7.560373012390942</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1787110602904551</v>
+        <v>0.0841143737538852</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.735353641939392</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.700558306579363</v>
+        <v>-7.937050022920786</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.03829894674719636</v>
+        <v>-0.05629773978937358</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.735353641939392</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.046433128564171</v>
+        <v>-8.282924844905594</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1039514169010318</v>
+        <v>-0.1985481034376018</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.735353641939392</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.35925792780915</v>
+        <v>-8.595749644150573</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2306764165440227</v>
+        <v>-0.3252731030805922</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.735353641939392</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.655919269619348</v>
+        <v>-8.892410985960771</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3455619773388938</v>
+        <v>-0.4401586638754633</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.804096777673271</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.089268377729583</v>
+        <v>-9.325760094071006</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5229279251173908</v>
+        <v>-0.6175246116539608</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.804096777673271</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.472269766472214</v>
+        <v>-9.708761482813637</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6762305819360273</v>
+        <v>-0.7708272684725972</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.804096777673271</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.847255092643492</v>
+        <v>-10.08374680898491</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.8236531964331082</v>
+        <v>-0.9182498829696777</v>
       </c>
       <c r="F1873" t="n">
         <v>-2.179082103844548</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.20678541514749</v>
+        <v>-10.44327713148892</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9621150221366586</v>
+        <v>-1.056711708673229</v>
       </c>
       <c r="F1874" t="n">
         <v>-2.179082103844548</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.53318544381251</v>
+        <v>-10.76967716015393</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.084759013645486</v>
+        <v>-1.179355700182056</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.505482132509561</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.7523344118867</v>
+        <v>-10.98882612822813</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.169376850253397</v>
+        <v>-1.263973536789966</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.724631100583759</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.74864348693029</v>
+        <v>-10.98513520327172</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.167900480270832</v>
+        <v>-1.262497166807402</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.724631100583759</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.95290166226016</v>
+        <v>-11.18939337860158</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.244090553284135</v>
+        <v>-1.338687239820705</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.852270045197748</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.17093943389133</v>
+        <v>-11.40743115023276</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.32682310745217</v>
+        <v>-1.42141979398874</v>
       </c>
       <c r="F1879" t="n">
         <v>-3.027040813293647</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.09746960222389</v>
+        <v>-11.33396131856531</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.282063473291769</v>
+        <v>-1.376660159828339</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.953570981626198</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.27259401961043</v>
+        <v>-11.50908573595185</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.33755801949887</v>
+        <v>-1.43215470603544</v>
       </c>
       <c r="F1881" t="n">
         <v>-3.128695399012742</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.50704611362492</v>
+        <v>-11.74353782996634</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.438558022006262</v>
+        <v>-1.533154708542832</v>
       </c>
       <c r="F1882" t="n">
         <v>-3.128695399012742</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.79484995816216</v>
+        <v>-12.03134167450358</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.560351750595134</v>
+        <v>-1.654948437131704</v>
       </c>
       <c r="F1883" t="n">
         <v>-3.41649924354998</v>
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.89189801645925</v>
+        <v>-12.2611661216674</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.598055184075416</v>
+        <v>-1.745762426158677</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.552669758134569</v>
+        <v>-3.579146780620141</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.027458591941292</v>
+        <v>1.011572378449949</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.12392693619551</v>
+        <v>-12.49319504140367</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.688173023340806</v>
+        <v>-1.835880265424068</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.614682455322992</v>
+        <v>-3.641159477808564</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9929447022573528</v>
+        <v>0.9770584887660094</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.0719114222267</v>
+        <v>-12.44117952743485</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.66337648206688</v>
+        <v>-1.811083724150141</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.614682455322992</v>
+        <v>-3.641159477808564</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.9969350379437536</v>
+        <v>0.9810488244524103</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.21358326395082</v>
+        <v>-12.58285136915897</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.72152044565527</v>
+        <v>-1.869227687738531</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.614682455322992</v>
+        <v>-3.641159477808564</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.9954598110450119</v>
+        <v>0.9795735975536686</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.3124900044101</v>
+        <v>-12.68175810961825</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.746029731674108</v>
+        <v>-1.893736973757369</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.713589195782267</v>
+        <v>-3.740066218267839</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.9511691769343189</v>
+        <v>0.9352829634429756</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.113337897173</v>
+        <v>-12.48260600238115</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.679420022425951</v>
+        <v>-1.827127264509212</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.548266669832454</v>
+        <v>-3.574743692318026</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.037311558857524</v>
+        <v>1.021425345366181</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.88749274445359</v>
+        <v>-12.25676084966174</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.579502888301978</v>
+        <v>-1.727210130385239</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.50633999424529</v>
+        <v>-3.532817016730863</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.072046637246031</v>
+        <v>1.056160423754688</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.60121793213089</v>
+        <v>-11.97048603733904</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.463853818816841</v>
+        <v>-1.611561060900102</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.50633999424529</v>
+        <v>-3.532817016730863</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.07318578180209</v>
+        <v>1.057299568310746</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.65411322017518</v>
+        <v>-12.02338132538333</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.482378159872448</v>
+        <v>-1.63008540195571</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.501384648156844</v>
+        <v>-3.527861670642416</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.078792763617265</v>
+        <v>1.062906550125922</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.37020448924643</v>
+        <v>-11.73947259445458</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.363080963262312</v>
+        <v>-1.510788205345573</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.501384648156844</v>
+        <v>-3.527861670642416</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.084526467855901</v>
+        <v>1.068640254364558</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.12321723905348</v>
+        <v>-11.49248534426163</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.274023325578996</v>
+        <v>-1.421730567662258</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.254397397963892</v>
+        <v>-3.280874420449464</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.222981555577808</v>
+        <v>1.207095342086464</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.85938037184941</v>
+        <v>-11.22864847705756</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.178372060010277</v>
+        <v>-1.326079302093537</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.254397397963892</v>
+        <v>-3.280874420449464</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.2130980742649</v>
+        <v>1.197211860773557</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.59213857098101</v>
+        <v>-10.96140667618916</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.073309900162291</v>
+        <v>-1.221017142245552</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.254397397963892</v>
+        <v>-3.280874420449464</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.211263513765526</v>
+        <v>1.195377300274183</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.31632940758053</v>
+        <v>-10.68559751278868</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.9632865497755581</v>
+        <v>-1.11099379185882</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.165378089685158</v>
+        <v>-3.191855112170731</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.264374783759306</v>
+        <v>1.248488570267962</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.29237586660457</v>
+        <v>-10.66164397181272</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.9530366272396811</v>
+        <v>-1.100743869322943</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.141424548709201</v>
+        <v>-3.167901571194773</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.279415414490374</v>
+        <v>1.26352920099903</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.02831592828177</v>
+        <v>-10.39758403348992</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.8606729680723149</v>
+        <v>-1.008380210155575</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.877364610386405</v>
+        <v>-2.903841632871977</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.424591061322299</v>
+        <v>1.408704847830956</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.321236304776935</v>
+        <v>-9.690504409985087</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.5806281523306804</v>
+        <v>-0.7283353944139419</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.877364610386405</v>
+        <v>-2.903841632871977</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.421804027661998</v>
+        <v>1.405917814170655</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.281052006410745</v>
+        <v>-9.650320111618896</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.5642108090963629</v>
+        <v>-0.7119180511796244</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.837180312020214</v>
+        <v>-2.863657334505787</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.446258230569554</v>
+        <v>1.430372017078211</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.20098221087294</v>
+        <v>-9.570250316081092</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.532816069660484</v>
+        <v>-0.6805233117437455</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.75711051648241</v>
+        <v>-2.783587538967982</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.493666929112994</v>
+        <v>1.47778071562165</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.967500988643341</v>
+        <v>-9.336769093851492</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.431499151930792</v>
+        <v>-0.5792063940140535</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.523629294252812</v>
+        <v>-2.550106316738384</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.641680091288605</v>
+        <v>1.625793877797262</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.787792458499467</v>
+        <v>-9.157060563707619</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3625079501862016</v>
+        <v>-0.5102151922694631</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.466457790090116</v>
+        <v>-2.492934812575688</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.673090783473263</v>
+        <v>1.65720456998192</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.65551698486858</v>
+        <v>-9.024785090076731</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3142302739868197</v>
+        <v>-0.4619375160700812</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.334182316459229</v>
+        <v>-2.360659338944802</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.747823554398822</v>
+        <v>1.731937340907479</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.464917310195426</v>
+        <v>-8.834185415403578</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2351753434299217</v>
+        <v>-0.3828825855131832</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.143582641786077</v>
+        <v>-2.170059664271649</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.864998419890351</v>
+        <v>1.849112206399007</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.215917511511845</v>
+        <v>-8.701352277122437</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1226690827328305</v>
+        <v>-0.3168429889770681</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.143582641786077</v>
+        <v>-2.170059664271649</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.877904761114009</v>
+        <v>1.862018547622666</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.32150750128495</v>
+        <v>-8.806942266895541</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2928810082412912</v>
+        <v>-0.4870549144855283</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.249172631559181</v>
+        <v>-2.275649654044754</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.686574837650928</v>
+        <v>1.670688624159584</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.340242403403547</v>
+        <v>-8.825677169014138</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2518306272116435</v>
+        <v>-0.4460045334558806</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.249172631559181</v>
+        <v>-2.275649654044754</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.735119179528014</v>
+        <v>1.719232966036671</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.063504228732734</v>
+        <v>-8.548938994343326</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1377563453573236</v>
+        <v>-0.3319302516015612</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.067355970449255</v>
+        <v>-2.093832992934828</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.847588188179965</v>
+        <v>1.831701974688621</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.936611822297664</v>
+        <v>-8.422046587908255</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.09571336903677397</v>
+        <v>-0.2898872752810111</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.940463564014185</v>
+        <v>-1.966940586499758</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.915009645787528</v>
+        <v>1.899123432296185</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.893063415526973</v>
+        <v>-8.378498181137564</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.08525461842359094</v>
+        <v>-0.2794285246678276</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.940463564014185</v>
+        <v>-1.966940586499758</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.908049033692435</v>
+        <v>1.892162820201092</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.650915022073115</v>
+        <v>-8.136349787683706</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.0260670933390954</v>
+        <v>-0.1681068129051413</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.940463564014185</v>
+        <v>-1.966940586499758</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.922511388073578</v>
+        <v>1.906625174582235</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.587685650304767</v>
+        <v>-8.073120415915358</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.04589096250562985</v>
+        <v>-0.1482829437386073</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.940463564014185</v>
+        <v>-1.966940586499758</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.917043508532773</v>
+        <v>1.90115729504143</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.401197957927761</v>
+        <v>-7.886632723538352</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1179841334670093</v>
+        <v>-0.07618977277722827</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.753975871637179</v>
+        <v>-1.780452894122752</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.026434217969554</v>
+        <v>2.01054800447821</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.380048759024318</v>
+        <v>-7.865483524634909</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1341447912657121</v>
+        <v>-0.06002911497852503</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.732826672733736</v>
+        <v>-1.759303695219308</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.046824715548945</v>
+        <v>2.030938502057602</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.136283317040873</v>
+        <v>-7.621718082651465</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2274316764061406</v>
+        <v>0.03325777016190345</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.732826672733736</v>
+        <v>-1.759303695219308</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.042605423895996</v>
+        <v>2.026719210404653</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.872255249847614</v>
+        <v>-7.357690015458205</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3351672172034603</v>
+        <v>0.1409933109592232</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.530961273917782</v>
+        <v>-1.557438296403355</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.165848977105584</v>
+        <v>2.149962763614241</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.622404855898539</v>
+        <v>-7.107839621509131</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4278494497667924</v>
+        <v>0.2336755435225553</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.530961273917782</v>
+        <v>-1.557438296403355</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.158591052089286</v>
+        <v>2.142704838597943</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.31883736689456</v>
+        <v>-6.804272132505152</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5528755688890326</v>
+        <v>0.3587016626447954</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.530961273917782</v>
+        <v>-1.557438296403355</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.162190175609935</v>
+        <v>2.146303962118592</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.245357458042546</v>
+        <v>-6.730792223653138</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.595595038484392</v>
+        <v>0.4014211322401544</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.457481365065768</v>
+        <v>-1.48395838755134</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.219605626975698</v>
+        <v>2.203719413484354</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.020324458373723</v>
+        <v>-6.505759223984315</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6846287159682181</v>
+        <v>0.4904548097239809</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.232448365396945</v>
+        <v>-1.258925387882517</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.353645904393288</v>
+        <v>2.337759690901945</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.805690080737317</v>
+        <v>-6.291124846347908</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7751772680770981</v>
+        <v>0.5810033618328609</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.017813987760538</v>
+        <v>-1.04429101024611</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.487121332029449</v>
+        <v>2.471235118538106</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.539089723762965</v>
+        <v>-6.024524489373556</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8630116696506347</v>
+        <v>0.6688377634063971</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.017813987760538</v>
+        <v>-1.04429101024611</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.468315590813245</v>
+        <v>2.452429377321902</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.298659226958105</v>
+        <v>-5.784093992568696</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.960926944997456</v>
+        <v>0.7667530387532189</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7773834909556778</v>
+        <v>-0.8038605134412502</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.614316965521039</v>
+        <v>2.598430752029695</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.055868419308659</v>
+        <v>-5.541303184919251</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.061972581892054</v>
+        <v>0.8677986756478169</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7773834909556778</v>
+        <v>-0.8038605134412502</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.618246279355859</v>
+        <v>2.602360065864516</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.81626332770157</v>
+        <v>-5.301698093312162</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.15849320245223</v>
+        <v>0.9643192962079925</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7103355432871833</v>
+        <v>-0.7368125657727557</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.659153631874295</v>
+        <v>2.643267418382952</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.573607739278406</v>
+        <v>-5.059042504888998</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.252553509041489</v>
+        <v>1.058379602797252</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7103355432871833</v>
+        <v>-0.7368125657727557</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.656151703094289</v>
+        <v>2.640265489602946</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.353586941241396</v>
+        <v>-4.839021706851987</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.342140865266907</v>
+        <v>1.14796695902267</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.569115698219203</v>
+        <v>-0.5955927207047754</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.742462647145691</v>
+        <v>2.726576433654348</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.154338311336587</v>
+        <v>-4.639773076947178</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.437734500030654</v>
+        <v>1.243560593786417</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.569115698219203</v>
+        <v>-0.5955927207047754</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.758356829947515</v>
+        <v>2.742470616456171</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>3.100972093319338</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.994823207817217</v>
+        <v>-4.480257973427809</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.502686385878704</v>
+        <v>1.308512479634467</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4096005946998331</v>
+        <v>-0.4360776171854055</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.855211736499438</v>
+        <v>2.839325523008095</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>3.111060195880778</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.85015106271748</v>
+        <v>-4.335585828328071</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.570643346480039</v>
+        <v>1.376469440235802</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2649284496000957</v>
+        <v>-0.2914054720856681</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.952103126120721</v>
+        <v>2.936216912629377</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>3.0263998879675</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.832381603786524</v>
+        <v>-4.317816369397115</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.493090822139143</v>
+        <v>1.298916915894905</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2471589906691402</v>
+        <v>-0.2736360131547125</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.878104493566016</v>
+        <v>2.862218280074672</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>3.048800381290066</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.745582106007515</v>
+        <v>-4.231016871618106</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.550211114573312</v>
+        <v>1.356037208329075</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2471589906691402</v>
+        <v>-0.2736360131547125</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.900504986888582</v>
+        <v>2.884618773397238</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.812618724905961</v>
+        <v>3.403317884538864</v>
       </c>
       <c r="C1935" t="n">
-        <v>3.219861282168526</v>
+        <v>2.92437550111035</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.745582106007515</v>
+        <v>-4.231016871618106</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.550211114573312</v>
+        <v>1.356037208329075</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2471589906691402</v>
+        <v>-0.2736360131547125</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.212925079154894</v>
+        <v>2.917439298096718</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240415.xlsx
+++ b/tame_output/ON/bt/strategyON_20240415.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.4%</t>
+          <t>-80.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>119.1%</t>
+          <t>119.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>139.6%</t>
+          <t>139.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.0%</t>
+          <t>97.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-58.7%</t>
+          <t>-58.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.2%</t>
+          <t>-76.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.9%</t>
+          <t>99.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>394.0%</t>
+          <t>385.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-584.7%</t>
+          <t>-571.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-29.2%</t>
+          <t>-25.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-18.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-240.6%</t>
+          <t>-235.2%</t>
         </is>
       </c>
     </row>
@@ -43940,10 +43940,10 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.188352630057362</v>
+        <v>-0.1687447661010623</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.050783243201093</v>
+        <v>3.058626388783613</v>
       </c>
       <c r="F1843" t="n">
         <v>1.711409540942887</v>
@@ -43963,10 +43963,10 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.2701245304851137</v>
+        <v>-0.250516666528814</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.008157208985231</v>
+        <v>3.016000354567751</v>
       </c>
       <c r="F1844" t="n">
         <v>1.738445114349024</v>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.3373336383569914</v>
+        <v>-0.3177257744006917</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.986038882670182</v>
+        <v>2.993882028252702</v>
       </c>
       <c r="F1845" t="n">
         <v>1.738445114349024</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.3333421855618012</v>
+        <v>-0.3137343216055015</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.985460259907498</v>
+        <v>2.993303405490018</v>
       </c>
       <c r="F1846" t="n">
         <v>1.742436567144214</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.7510962091086382</v>
+        <v>-0.7314883451523384</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.816285541993827</v>
+        <v>2.824128687576347</v>
       </c>
       <c r="F1847" t="n">
         <v>1.324682543597377</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.9727181426667557</v>
+        <v>-0.9531102787104559</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.727502985169502</v>
+        <v>2.735346130752021</v>
       </c>
       <c r="F1848" t="n">
         <v>1.287156409910008</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.180722201019833</v>
+        <v>-1.161114337063533</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.649193506382196</v>
+        <v>2.657036651964716</v>
       </c>
       <c r="F1849" t="n">
         <v>1.287156409910008</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.451122163728718</v>
+        <v>-1.431514299772419</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.53611497763663</v>
+        <v>2.54395812321915</v>
       </c>
       <c r="F1850" t="n">
         <v>1.016756447201123</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.79028054131724</v>
+        <v>-1.770672677360941</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.39353592590767</v>
+        <v>2.40137907149019</v>
       </c>
       <c r="F1851" t="n">
         <v>0.6775980696126005</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.118297763044719</v>
+        <v>-2.09868989908842</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.282667326955447</v>
+        <v>2.290510472537967</v>
       </c>
       <c r="F1852" t="n">
         <v>0.3495808478851213</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.611622634579897</v>
+        <v>-2.592014770623598</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.093436128749944</v>
+        <v>2.101279274332464</v>
       </c>
       <c r="F1853" t="n">
         <v>0.2445947336455026</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.104007662603994</v>
+        <v>-3.084399798647695</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.897588509584037</v>
+        <v>1.905431655166557</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.2477902943785941</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.489188053534066</v>
+        <v>-3.469580189577767</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.742058892024872</v>
+        <v>1.749902037607392</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.2477902943785941</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.832870826760729</v>
+        <v>-3.81326296280443</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.606354906188823</v>
+        <v>1.614198051771343</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.3556963464058123</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.190521176999077</v>
+        <v>-4.170913313042778</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.459400824749741</v>
+        <v>1.467243970332262</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.7133466966441604</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.499755279995128</v>
+        <v>-4.480147416038829</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.337480110251581</v>
+        <v>1.345323255834101</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.7133466966441604</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.931561073144915</v>
+        <v>-4.911953209188616</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.15109068045907</v>
+        <v>1.15893382604159</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.8497641930854274</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.257993602012659</v>
+        <v>-5.23838573805636</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.008802443914063</v>
+        <v>1.016645589496583</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.9322324435925755</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.593656249243112</v>
+        <v>-5.574048385286813</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8731179766778472</v>
+        <v>0.8809611222603673</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.9322324435925755</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.957282494143425</v>
+        <v>-5.937674630187126</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7341550389519638</v>
+        <v>0.7419981845344834</v>
       </c>
       <c r="F1862" t="n">
         <v>-1.030454080459701</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.322409876782172</v>
+        <v>-6.302802012825873</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5873586009022964</v>
+        <v>0.5952017464848161</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.326764864758714</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.730998653962851</v>
+        <v>-6.711390790006551</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4226846340447836</v>
+        <v>0.4305277796273042</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.735353641939392</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.143981138103944</v>
+        <v>-7.124373274147644</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2526770728598069</v>
+        <v>0.260520218442327</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.735353641939392</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.560373012390942</v>
+        <v>-7.540765148434642</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.0841143737538852</v>
+        <v>0.09195751933640572</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.735353641939392</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.937050022920786</v>
+        <v>-7.917442158964486</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.05629773978937358</v>
+        <v>-0.04845459420685305</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.735353641939392</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.282924844905594</v>
+        <v>-8.263316980949295</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1985481034376018</v>
+        <v>-0.1907049578550812</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.735353641939392</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.595749644150573</v>
+        <v>-8.576141780194273</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.3252731030805922</v>
+        <v>-0.3174299574980721</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.735353641939392</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.892410985960771</v>
+        <v>-8.872803122004472</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4401586638754633</v>
+        <v>-0.4323155182929432</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.804096777673271</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.325760094071006</v>
+        <v>-9.306152230114707</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.6175246116539608</v>
+        <v>-0.6096814660714402</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.804096777673271</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.708761482813637</v>
+        <v>-9.689153618857338</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7708272684725972</v>
+        <v>-0.7629841228900767</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.804096777673271</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-10.08374680898491</v>
+        <v>-10.06413894502862</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.9182498829696777</v>
+        <v>-0.9104067373871572</v>
       </c>
       <c r="F1873" t="n">
         <v>-2.179082103844548</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.44327713148892</v>
+        <v>-10.42366926753262</v>
       </c>
       <c r="E1874" t="n">
-        <v>-1.056711708673229</v>
+        <v>-1.048868563090708</v>
       </c>
       <c r="F1874" t="n">
         <v>-2.179082103844548</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.76967716015393</v>
+        <v>-10.75006929619763</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.179355700182056</v>
+        <v>-1.171512554599536</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.505482132509561</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.98882612822813</v>
+        <v>-10.96921826427183</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.263973536789966</v>
+        <v>-1.256130391207446</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.724631100583759</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.98513520327172</v>
+        <v>-10.96552733931542</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.262497166807402</v>
+        <v>-1.254654021224881</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.724631100583759</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-11.18939337860158</v>
+        <v>-11.16978551464528</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.338687239820705</v>
+        <v>-1.330844094238184</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.852270045197748</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.40743115023276</v>
+        <v>-11.38782328627646</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.42141979398874</v>
+        <v>-1.41357664840622</v>
       </c>
       <c r="F1879" t="n">
         <v>-3.027040813293647</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.33396131856531</v>
+        <v>-11.31435345460901</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.376660159828339</v>
+        <v>-1.368817014245819</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.953570981626198</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.50908573595185</v>
+        <v>-11.48947787199555</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.43215470603544</v>
+        <v>-1.424311560452919</v>
       </c>
       <c r="F1881" t="n">
         <v>-3.128695399012742</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.74353782996634</v>
+        <v>-11.72392996601004</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.533154708542832</v>
+        <v>-1.525311562960311</v>
       </c>
       <c r="F1882" t="n">
         <v>-3.128695399012742</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-12.03134167450358</v>
+        <v>-12.01173381054728</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.654948437131704</v>
+        <v>-1.647105291549183</v>
       </c>
       <c r="F1883" t="n">
         <v>-3.41649924354998</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.2611661216674</v>
+        <v>-12.24155825771111</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.745762426158677</v>
+        <v>-1.737919280576157</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.579146780620141</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.49319504140367</v>
+        <v>-12.47358717744737</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.835880265424068</v>
+        <v>-1.828037119841547</v>
       </c>
       <c r="F1885" t="n">
         <v>-3.641159477808564</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.44117952743485</v>
+        <v>-12.42157166347855</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.811083724150141</v>
+        <v>-1.803240578567621</v>
       </c>
       <c r="F1886" t="n">
         <v>-3.641159477808564</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.58285136915897</v>
+        <v>-12.56324350520267</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.869227687738531</v>
+        <v>-1.861384542156011</v>
       </c>
       <c r="F1887" t="n">
         <v>-3.641159477808564</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.68175810961825</v>
+        <v>-12.66215024566195</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.893736973757369</v>
+        <v>-1.885893828174849</v>
       </c>
       <c r="F1888" t="n">
         <v>-3.740066218267839</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.48260600238115</v>
+        <v>-12.46299813842485</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.827127264509212</v>
+        <v>-1.819284118926692</v>
       </c>
       <c r="F1889" t="n">
         <v>-3.574743692318026</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.25676084966174</v>
+        <v>-12.23715298570544</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.727210130385239</v>
+        <v>-1.719366984802719</v>
       </c>
       <c r="F1890" t="n">
         <v>-3.532817016730863</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.97048603733904</v>
+        <v>-11.95087817338274</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.611561060900102</v>
+        <v>-1.603717915317582</v>
       </c>
       <c r="F1891" t="n">
         <v>-3.532817016730863</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-12.02338132538333</v>
+        <v>-12.00377346142703</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.63008540195571</v>
+        <v>-1.622242256373188</v>
       </c>
       <c r="F1892" t="n">
         <v>-3.527861670642416</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.73947259445458</v>
+        <v>-11.71986473049828</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.510788205345573</v>
+        <v>-1.502945059763053</v>
       </c>
       <c r="F1893" t="n">
         <v>-3.527861670642416</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.49248534426163</v>
+        <v>-11.47287748030533</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.421730567662258</v>
+        <v>-1.413887422079737</v>
       </c>
       <c r="F1894" t="n">
         <v>-3.280874420449464</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.22864847705756</v>
+        <v>-11.20904061310126</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.326079302093537</v>
+        <v>-1.318236156511017</v>
       </c>
       <c r="F1895" t="n">
         <v>-3.280874420449464</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.96140667618916</v>
+        <v>-10.94179881223286</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.221017142245552</v>
+        <v>-1.213173996663031</v>
       </c>
       <c r="F1896" t="n">
         <v>-3.280874420449464</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.68559751278868</v>
+        <v>-10.66598964883238</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.11099379185882</v>
+        <v>-1.103150646276298</v>
       </c>
       <c r="F1897" t="n">
         <v>-3.191855112170731</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.66164397181272</v>
+        <v>-10.64203610785642</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.100743869322943</v>
+        <v>-1.092900723740421</v>
       </c>
       <c r="F1898" t="n">
         <v>-3.167901571194773</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.39758403348992</v>
+        <v>-10.37797616953362</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.008380210155575</v>
+        <v>-1.000537064573055</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.903841632871977</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.690504409985087</v>
+        <v>-9.670896546028786</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7283353944139419</v>
+        <v>-0.7204922488314205</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.903841632871977</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.650320111618896</v>
+        <v>-9.630712247662595</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7119180511796244</v>
+        <v>-0.704074905597103</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.863657334505787</v>
@@ -45297,10 +45297,10 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.570250316081092</v>
+        <v>-9.550642452124791</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6805233117437455</v>
+        <v>-0.6726801661612245</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.783587538967982</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.336769093851492</v>
+        <v>-9.317161229895191</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5792063940140535</v>
+        <v>-0.5713632484315321</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.550106316738384</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.157060563707619</v>
+        <v>-9.137452699751318</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5102151922694631</v>
+        <v>-0.5023720466869421</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.492934812575688</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.024785090076731</v>
+        <v>-9.005177226120431</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4619375160700812</v>
+        <v>-0.4540943704875602</v>
       </c>
       <c r="F1905" t="n">
         <v>-2.360659338944802</v>
@@ -45389,10 +45389,10 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.834185415403578</v>
+        <v>-8.814577551447277</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3828825855131832</v>
+        <v>-0.3750394399306618</v>
       </c>
       <c r="F1906" t="n">
         <v>-2.170059664271649</v>
@@ -45412,10 +45412,10 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.701352277122437</v>
+        <v>-8.565577752763696</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.3168429889770681</v>
+        <v>-0.262533179233571</v>
       </c>
       <c r="F1907" t="n">
         <v>-2.170059664271649</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.806942266895541</v>
+        <v>-8.671167742536801</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4870549144855283</v>
+        <v>-0.4327451047420312</v>
       </c>
       <c r="F1908" t="n">
         <v>-2.275649654044754</v>
@@ -45458,10 +45458,10 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.825677169014138</v>
+        <v>-8.689902644655398</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4460045334558806</v>
+        <v>-0.3916947237123836</v>
       </c>
       <c r="F1909" t="n">
         <v>-2.275649654044754</v>
@@ -45481,10 +45481,10 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.548938994343326</v>
+        <v>-8.413164469984585</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.3319302516015612</v>
+        <v>-0.2776204418580641</v>
       </c>
       <c r="F1910" t="n">
         <v>-2.093832992934828</v>
@@ -45504,10 +45504,10 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.422046587908255</v>
+        <v>-8.286272063549514</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2898872752810111</v>
+        <v>-0.235577465537514</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.966940586499758</v>
@@ -45527,10 +45527,10 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.378498181137564</v>
+        <v>-8.242723656778823</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2794285246678276</v>
+        <v>-0.2251187149243306</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.966940586499758</v>
@@ -45550,10 +45550,10 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.136349787683706</v>
+        <v>-8.000575263324965</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1681068129051413</v>
+        <v>-0.1137970031616442</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.966940586499758</v>
@@ -45573,10 +45573,10 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.073120415915358</v>
+        <v>-7.937345891556617</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1482829437386073</v>
+        <v>-0.09397313399510976</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.966940586499758</v>
@@ -45596,10 +45596,10 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.886632723538352</v>
+        <v>-7.750858199179611</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.07618977277722827</v>
+        <v>-0.02187996303373074</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.780452894122752</v>
@@ -45619,10 +45619,10 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.865483524634909</v>
+        <v>-7.729709000276167</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.06002911497852503</v>
+        <v>-0.005719305235027505</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.759303695219308</v>
@@ -45642,10 +45642,10 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.621718082651465</v>
+        <v>-7.485943558292723</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.03325777016190345</v>
+        <v>0.08756757990540054</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.759303695219308</v>
@@ -45665,10 +45665,10 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.357690015458205</v>
+        <v>-7.221915491099463</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1409933109592232</v>
+        <v>0.1953031207027207</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.557438296403355</v>
@@ -45688,10 +45688,10 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.107839621509131</v>
+        <v>-6.972065097150388</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2336755435225553</v>
+        <v>0.2879853532660528</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.557438296403355</v>
@@ -45711,10 +45711,10 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.804272132505152</v>
+        <v>-6.668497608146409</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3587016626447954</v>
+        <v>0.4130114723882929</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.557438296403355</v>
@@ -45734,10 +45734,10 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.730792223653138</v>
+        <v>-6.595017699294395</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4014211322401544</v>
+        <v>0.4557309419836524</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.48395838755134</v>
@@ -45757,10 +45757,10 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.505759223984315</v>
+        <v>-6.369984699625572</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4904548097239809</v>
+        <v>0.5447646194674785</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.258925387882517</v>
@@ -45780,10 +45780,10 @@
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.291124846347908</v>
+        <v>-6.155350321989165</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5810033618328609</v>
+        <v>0.6353131715763585</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.04429101024611</v>
@@ -45803,10 +45803,10 @@
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.024524489373556</v>
+        <v>-5.888749965014814</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6688377634063971</v>
+        <v>0.7231475731498951</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.04429101024611</v>
@@ -45826,10 +45826,10 @@
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.784093992568696</v>
+        <v>-5.648319468209953</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7667530387532189</v>
+        <v>0.8210628484967164</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.8038605134412502</v>
@@ -45849,10 +45849,10 @@
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.541303184919251</v>
+        <v>-5.405528660560508</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8677986756478169</v>
+        <v>0.9221084853913148</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.8038605134412502</v>
@@ -45872,10 +45872,10 @@
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.301698093312162</v>
+        <v>-5.165923568953419</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9643192962079925</v>
+        <v>1.01862910595149</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.7368125657727557</v>
@@ -45895,10 +45895,10 @@
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.059042504888998</v>
+        <v>-4.923267980530255</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.058379602797252</v>
+        <v>1.112689412540749</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.7368125657727557</v>
@@ -45918,10 +45918,10 @@
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.839021706851987</v>
+        <v>-4.703247182493245</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.14796695902267</v>
+        <v>1.202276768766168</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.5955927207047754</v>
@@ -45941,10 +45941,10 @@
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.639773076947178</v>
+        <v>-4.503998552588436</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.243560593786417</v>
+        <v>1.297870403529915</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.5955927207047754</v>
@@ -45964,10 +45964,10 @@
         <v>3.100972093319338</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.480257973427809</v>
+        <v>-4.344483449069066</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.308512479634467</v>
+        <v>1.362822289377964</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.4360776171854055</v>
@@ -45987,10 +45987,10 @@
         <v>3.111060195880778</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.335585828328071</v>
+        <v>-4.199811303969328</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.376469440235802</v>
+        <v>1.430779249979299</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.2914054720856681</v>
@@ -46010,10 +46010,10 @@
         <v>3.0263998879675</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.317816369397115</v>
+        <v>-4.182041845038373</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.298916915894905</v>
+        <v>1.353226725638403</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.2736360131547125</v>
@@ -46033,10 +46033,10 @@
         <v>3.048800381290066</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.231016871618106</v>
+        <v>-4.095242347259363</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.356037208329075</v>
+        <v>1.410347018072573</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.2736360131547125</v>
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.403317884538864</v>
+        <v>3.403317884538865</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.92437550111035</v>
+        <v>2.924375501110351</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.231016871618106</v>
+        <v>-4.095242347259363</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.356037208329075</v>
+        <v>1.410347018072573</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.2736360131547125</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.917439298096718</v>
+        <v>2.917439298096719</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240415.xlsx
+++ b/tame_output/ON/bt/strategyON_20240415.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>54.8%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -819,12 +819,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-19.2%</t>
+          <t>-6.7%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.0%</t>
+          <t>-79.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>119.4%</t>
+          <t>118.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>139.5%</t>
+          <t>138.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-722.5%</t>
+          <t>-708.7%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-58.6%</t>
+          <t>-57.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.6%</t>
+          <t>-74.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>98.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>385.7%</t>
+          <t>754.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-571.1%</t>
+          <t>-552.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-283.6%</t>
+          <t>-278.1%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.9%</t>
+          <t>-44.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-25.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-18.7%</t>
+          <t>167.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-235.2%</t>
+          <t>-227.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.1%</t>
+          <t>-31.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>72.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>73.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.5%</t>
+          <t>-37.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.2%</t>
+          <t>-24.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.6%</t>
+          <t>-147.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-251.4%</t>
+          <t>-258.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>97.9%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.2%</t>
+          <t>-32.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-154.3%</t>
+          <t>-161.8%</t>
         </is>
       </c>
     </row>
@@ -43940,10 +43940,10 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.1687447661010623</v>
+        <v>0.04813908628406116</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.058626388783613</v>
+        <v>3.145379929737663</v>
       </c>
       <c r="F1843" t="n">
         <v>1.711409540942887</v>
@@ -43957,16 +43957,16 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.29873059070667</v>
+        <v>3.298730590706671</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.250516666528814</v>
+        <v>-0.03363281414369051</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.016000354567751</v>
+        <v>3.1027538955218</v>
       </c>
       <c r="F1844" t="n">
         <v>1.738445114349024</v>
@@ -43980,16 +43980,16 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296837</v>
+        <v>3.299918119296838</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.3177257744006917</v>
+        <v>-0.1008419220155682</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.993882028252702</v>
+        <v>3.080635569206751</v>
       </c>
       <c r="F1845" t="n">
         <v>1.738445114349024</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201488</v>
+        <v>3.295507330201489</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.3137343216055015</v>
+        <v>-0.09685046922037799</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.993303405490018</v>
+        <v>3.080056946444068</v>
       </c>
       <c r="F1846" t="n">
         <v>1.742436567144214</v>
@@ -44026,16 +44026,16 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153007</v>
+        <v>3.258791981153008</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.7314883451523384</v>
+        <v>-0.514604492767215</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.824128687576347</v>
+        <v>2.910882228530396</v>
       </c>
       <c r="F1847" t="n">
         <v>1.324682543597377</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537426</v>
+        <v>3.271168579537427</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.9531102787104559</v>
+        <v>-0.7362264263253324</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.735346130752021</v>
+        <v>2.822099671706071</v>
       </c>
       <c r="F1848" t="n">
         <v>1.287156409910008</v>
@@ -44072,16 +44072,16 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382192</v>
+        <v>3.272760131382193</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.161114337063533</v>
+        <v>-0.9442304846784096</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.657036651964716</v>
+        <v>2.743790192918765</v>
       </c>
       <c r="F1849" t="n">
         <v>1.287156409910008</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.431514299772419</v>
+        <v>-1.214630447387295</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.54395812321915</v>
+        <v>2.630711664173199</v>
       </c>
       <c r="F1850" t="n">
         <v>1.016756447201123</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.770672677360941</v>
+        <v>-1.553788824975817</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.40137907149019</v>
+        <v>2.48813261244424</v>
       </c>
       <c r="F1851" t="n">
         <v>0.6775980696126005</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.09868989908842</v>
+        <v>-1.881806046703296</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.290510472537967</v>
+        <v>2.377264013492016</v>
       </c>
       <c r="F1852" t="n">
         <v>0.3495808478851213</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.592014770623598</v>
+        <v>-2.375130918238474</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.101279274332464</v>
+        <v>2.188032815286514</v>
       </c>
       <c r="F1853" t="n">
         <v>0.2445947336455026</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.084399798647695</v>
+        <v>-2.867515946262571</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.905431655166557</v>
+        <v>1.992185196120607</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.2477902943785941</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.469580189577767</v>
+        <v>-3.252696337192643</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.749902037607392</v>
+        <v>1.836655578561441</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.2477902943785941</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.81326296280443</v>
+        <v>-3.596379110419306</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.614198051771343</v>
+        <v>1.700951592725392</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.3556963464058123</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.170913313042778</v>
+        <v>-3.954029460657654</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.467243970332262</v>
+        <v>1.553997511286311</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.7133466966441604</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.480147416038829</v>
+        <v>-4.263263563653705</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.345323255834101</v>
+        <v>1.43207679678815</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.7133466966441604</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.911953209188616</v>
+        <v>-4.695069356803493</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.15893382604159</v>
+        <v>1.245687366995639</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.8497641930854274</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.23838573805636</v>
+        <v>-5.021501885671237</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.016645589496583</v>
+        <v>1.103399130450633</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.9322324435925755</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.574048385286813</v>
+        <v>-5.357164532901689</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8809611222603673</v>
+        <v>0.9677146632144167</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.9322324435925755</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.937674630187126</v>
+        <v>-5.720790777802002</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7419981845344834</v>
+        <v>0.8287517254885328</v>
       </c>
       <c r="F1862" t="n">
         <v>-1.030454080459701</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.302802012825873</v>
+        <v>-6.085918160440749</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5952017464848161</v>
+        <v>0.6819552874388655</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.326764864758714</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.711390790006551</v>
+        <v>-6.494506937621427</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4305277796273042</v>
+        <v>0.5172813205813536</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.735353641939392</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.124373274147644</v>
+        <v>-6.907489421762521</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.260520218442327</v>
+        <v>0.3472737593963764</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.735353641939392</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.540765148434642</v>
+        <v>-7.323881296049518</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.09195751933640572</v>
+        <v>0.1787110602904551</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.735353641939392</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.917442158964486</v>
+        <v>-7.700558306579363</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.04845459420685305</v>
+        <v>0.03829894674719636</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.735353641939392</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.263316980949295</v>
+        <v>-8.046433128564171</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1907049578550812</v>
+        <v>-0.1039514169010318</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.735353641939392</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.576141780194273</v>
+        <v>-8.35925792780915</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.3174299574980721</v>
+        <v>-0.2306764165440227</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.735353641939392</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.872803122004472</v>
+        <v>-8.655919269619348</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4323155182929432</v>
+        <v>-0.3455619773388938</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.804096777673271</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.306152230114707</v>
+        <v>-9.089268377729583</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.6096814660714402</v>
+        <v>-0.5229279251173908</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.804096777673271</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.689153618857338</v>
+        <v>-9.472269766472214</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7629841228900767</v>
+        <v>-0.6762305819360273</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.804096777673271</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-10.06413894502862</v>
+        <v>-9.847255092643492</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.9104067373871572</v>
+        <v>-0.8236531964331082</v>
       </c>
       <c r="F1873" t="n">
         <v>-2.179082103844548</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.42366926753262</v>
+        <v>-10.20678541514749</v>
       </c>
       <c r="E1874" t="n">
-        <v>-1.048868563090708</v>
+        <v>-0.9621150221366586</v>
       </c>
       <c r="F1874" t="n">
         <v>-2.179082103844548</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.75006929619763</v>
+        <v>-10.53318544381251</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.171512554599536</v>
+        <v>-1.084759013645486</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.505482132509561</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.96921826427183</v>
+        <v>-10.7523344118867</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.256130391207446</v>
+        <v>-1.169376850253397</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.724631100583759</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.96552733931542</v>
+        <v>-10.74864348693029</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.254654021224881</v>
+        <v>-1.167900480270832</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.724631100583759</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-11.16978551464528</v>
+        <v>-10.95290166226016</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.330844094238184</v>
+        <v>-1.244090553284135</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.852270045197748</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.38782328627646</v>
+        <v>-11.17093943389133</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.41357664840622</v>
+        <v>-1.32682310745217</v>
       </c>
       <c r="F1879" t="n">
         <v>-3.027040813293647</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.31435345460901</v>
+        <v>-11.09746960222389</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.368817014245819</v>
+        <v>-1.282063473291769</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.953570981626198</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.48947787199555</v>
+        <v>-11.27259401961043</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.424311560452919</v>
+        <v>-1.33755801949887</v>
       </c>
       <c r="F1881" t="n">
         <v>-3.128695399012742</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.72392996601004</v>
+        <v>-11.50704611362492</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.525311562960311</v>
+        <v>-1.438558022006262</v>
       </c>
       <c r="F1882" t="n">
         <v>-3.128695399012742</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-12.01173381054728</v>
+        <v>-11.79484995816216</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.647105291549183</v>
+        <v>-1.560351750595134</v>
       </c>
       <c r="F1883" t="n">
         <v>-3.41649924354998</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.24155825771111</v>
+        <v>-12.02467440532598</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.737919280576157</v>
+        <v>-1.651165739622107</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.579146780620141</v>
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767394</v>
+        <v>3.492098065767395</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.47358717744737</v>
+        <v>-12.11934568980972</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.828037119841547</v>
+        <v>-1.68634052478649</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.641159477808564</v>
+        <v>-3.540754613335595</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9770584887660094</v>
+        <v>1.037301407449791</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.42157166347855</v>
+        <v>-12.06733017584091</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.803240578567621</v>
+        <v>-1.661543983512564</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.641159477808564</v>
+        <v>-3.540754613335595</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.9810488244524103</v>
+        <v>1.041291743136191</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.56324350520267</v>
+        <v>-12.20900201756503</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.861384542156011</v>
+        <v>-1.719687947100954</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.641159477808564</v>
+        <v>-3.540754613335595</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.9795735975536686</v>
+        <v>1.03981651623745</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.66215024566195</v>
+        <v>-12.30790875802431</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.885893828174849</v>
+        <v>-1.744197233119791</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.740066218267839</v>
+        <v>-3.639661353794871</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.9352829634429756</v>
+        <v>0.9955258821267572</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240574</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.46299813842485</v>
+        <v>-12.10875665078721</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.819284118926692</v>
+        <v>-1.677587523871635</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.574743692318026</v>
+        <v>-3.474338827845057</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.021425345366181</v>
+        <v>1.081668264049962</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.23715298570544</v>
+        <v>-11.8829114980678</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.719366984802719</v>
+        <v>-1.577670389747662</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.532817016730863</v>
+        <v>-3.432412152257894</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.056160423754688</v>
+        <v>1.116403342438469</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.95087817338274</v>
+        <v>-11.5966366857451</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.603717915317582</v>
+        <v>-1.462021320262525</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.532817016730863</v>
+        <v>-3.432412152257894</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.057299568310746</v>
+        <v>1.117542486994528</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-12.00377346142703</v>
+        <v>-11.64953197378939</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.622242256373188</v>
+        <v>-1.480545661318132</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.527861670642416</v>
+        <v>-3.427456806169447</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.062906550125922</v>
+        <v>1.123149468809703</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.71986473049828</v>
+        <v>-11.36562324286064</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.502945059763053</v>
+        <v>-1.361248464707996</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.527861670642416</v>
+        <v>-3.427456806169447</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.068640254364558</v>
+        <v>1.12888317304834</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.47287748030533</v>
+        <v>-11.11863599266769</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.413887422079737</v>
+        <v>-1.272190827024681</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.280874420449464</v>
+        <v>-3.180469555976495</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.207095342086464</v>
+        <v>1.267338260770245</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.20904061310126</v>
+        <v>-10.85479912546362</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.318236156511017</v>
+        <v>-1.17653956145596</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.280874420449464</v>
+        <v>-3.180469555976495</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.197211860773557</v>
+        <v>1.257454779457338</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.94179881223286</v>
+        <v>-10.58755732459522</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.213173996663031</v>
+        <v>-1.071477401607975</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.280874420449464</v>
+        <v>-3.180469555976495</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.195377300274183</v>
+        <v>1.255620218957964</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.66598964883238</v>
+        <v>-10.31174816119474</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.103150646276298</v>
+        <v>-0.9614540512212417</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.191855112170731</v>
+        <v>-3.091450247697762</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.248488570267962</v>
+        <v>1.308731488951744</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.64203610785642</v>
+        <v>-10.28779462021878</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.092900723740421</v>
+        <v>-0.9512041286853647</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.167901571194773</v>
+        <v>-3.067496706721804</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.26352920099903</v>
+        <v>1.323772119682812</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.37797616953362</v>
+        <v>-10.02373468189598</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.000537064573055</v>
+        <v>-0.8588404695179985</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.903841632871977</v>
+        <v>-2.803436768399008</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.408704847830956</v>
+        <v>1.468947766514737</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.670896546028786</v>
+        <v>-9.316655058391145</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7204922488314205</v>
+        <v>-0.5787956537763645</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.903841632871977</v>
+        <v>-2.803436768399008</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.405917814170655</v>
+        <v>1.466160732854436</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.630712247662595</v>
+        <v>-9.276470760024955</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.704074905597103</v>
+        <v>-0.562378310542047</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.863657334505787</v>
+        <v>-2.763252470032818</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.430372017078211</v>
+        <v>1.490614935761992</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.550642452124791</v>
+        <v>-9.19640096448715</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6726801661612245</v>
+        <v>-0.5309835711061681</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.783587538967982</v>
+        <v>-2.683182674495014</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.47778071562165</v>
+        <v>1.538023634305431</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.317161229895191</v>
+        <v>-8.962919742257551</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5713632484315321</v>
+        <v>-0.4296666533764761</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.550106316738384</v>
+        <v>-2.449701452265415</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.625793877797262</v>
+        <v>1.686036796481043</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.137452699751318</v>
+        <v>-8.783211212113677</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5023720466869421</v>
+        <v>-0.3606754516318857</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.492934812575688</v>
+        <v>-2.392529948102719</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.65720456998192</v>
+        <v>1.717447488665701</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.005177226120431</v>
+        <v>-8.65093573848279</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4540943704875602</v>
+        <v>-0.3123977754325038</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.360659338944802</v>
+        <v>-2.260254474471833</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.731937340907479</v>
+        <v>1.79218025959126</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.814577551447277</v>
+        <v>-8.460336063809637</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3750394399306618</v>
+        <v>-0.2333428448756059</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.170059664271649</v>
+        <v>-2.06965479979868</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.849112206399007</v>
+        <v>1.909355125082788</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.565577752763696</v>
+        <v>-8.211336265126056</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.262533179233571</v>
+        <v>-0.1208365841785146</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.170059664271649</v>
+        <v>-2.06965479979868</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.862018547622666</v>
+        <v>1.922261466306447</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077643</v>
+        <v>3.692928280077642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.671167742536801</v>
+        <v>-8.31692625489916</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4327451047420312</v>
+        <v>-0.2910485096869753</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.275649654044754</v>
+        <v>-2.175244789571785</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.670688624159584</v>
+        <v>1.730931542843366</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.7704190084579</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.689902644655398</v>
+        <v>-8.335661157017757</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3916947237123836</v>
+        <v>-0.2499981286573276</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.275649654044754</v>
+        <v>-2.175244789571785</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.719232966036671</v>
+        <v>1.779475884720452</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180808</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.413164469984585</v>
+        <v>-8.058922982346944</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2776204418580641</v>
+        <v>-0.1359238468030077</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.093832992934828</v>
+        <v>-1.993428128461859</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.831701974688621</v>
+        <v>1.891944893372402</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.286272063549514</v>
+        <v>-7.932030575911874</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.235577465537514</v>
+        <v>-0.09388087048245763</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.966940586499758</v>
+        <v>-1.866535722026789</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.899123432296185</v>
+        <v>1.959366350979966</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568105</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.242723656778823</v>
+        <v>-7.888482169141183</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2251187149243306</v>
+        <v>-0.08342211986927461</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.966940586499758</v>
+        <v>-1.866535722026789</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.892162820201092</v>
+        <v>1.952405738884873</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963416</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.000575263324965</v>
+        <v>-7.646333775687325</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1137970031616442</v>
+        <v>0.02789959189341173</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.966940586499758</v>
+        <v>-1.866535722026789</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.906625174582235</v>
+        <v>1.966868093266016</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192814</v>
+        <v>3.828547911192812</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.937345891556617</v>
+        <v>-7.583104403918977</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.09397313399510976</v>
+        <v>0.04772346105994574</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.966940586499758</v>
+        <v>-1.866535722026789</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.90115729504143</v>
+        <v>1.961400213725211</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262044</v>
+        <v>3.828049353262042</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.750858199179611</v>
+        <v>-7.396616711541971</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.02187996303373074</v>
+        <v>0.1198166320213252</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.780452894122752</v>
+        <v>-1.680048029649783</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.01054800447821</v>
+        <v>2.070790923161992</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389906</v>
+        <v>3.812450103389905</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.729709000276167</v>
+        <v>-7.375467512638528</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.005719305235027505</v>
+        <v>0.135977289820028</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.759303695219308</v>
+        <v>-1.658898830746339</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.030938502057602</v>
+        <v>2.091181420741383</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788091</v>
+        <v>3.74832483278809</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.485943558292723</v>
+        <v>-7.131702070655083</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.08756757990540054</v>
+        <v>0.2292641749604565</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.759303695219308</v>
+        <v>-1.658898830746339</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.026719210404653</v>
+        <v>2.086962129088434</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527523</v>
+        <v>3.824307657527522</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.221915491099463</v>
+        <v>-6.867674003461824</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1953031207027207</v>
+        <v>0.3369997157577762</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.557438296403355</v>
+        <v>-1.457033431930386</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.149962763614241</v>
+        <v>2.210205682298022</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749182</v>
+        <v>3.826351398749181</v>
       </c>
       <c r="C1919" t="n">
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.972065097150388</v>
+        <v>-6.617823609512749</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2879853532660528</v>
+        <v>0.4296819483211083</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.557438296403355</v>
+        <v>-1.457033431930386</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.142704838597943</v>
+        <v>2.202947757281724</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481495</v>
+        <v>3.835954411481494</v>
       </c>
       <c r="C1920" t="n">
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.668497608146409</v>
+        <v>-6.31425612050877</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4130114723882929</v>
+        <v>0.5547080674433484</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.557438296403355</v>
+        <v>-1.457033431930386</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.146303962118592</v>
+        <v>2.206546880802373</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862984</v>
+        <v>3.780930335862983</v>
       </c>
       <c r="C1921" t="n">
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.595017699294395</v>
+        <v>-6.240776211656756</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4557309419836524</v>
+        <v>0.5974275370387079</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.48395838755134</v>
+        <v>-1.383553523078371</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.203719413484354</v>
+        <v>2.263962332168135</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102779</v>
+        <v>3.773761647102778</v>
       </c>
       <c r="C1922" t="n">
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.369984699625572</v>
+        <v>-6.015743211987933</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5447646194674785</v>
+        <v>0.6864612145225339</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.258925387882517</v>
+        <v>-1.158520523409548</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.337759690901945</v>
+        <v>2.398002609585726</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353072</v>
+        <v>3.764614304353071</v>
       </c>
       <c r="C1923" t="n">
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.155350321989165</v>
+        <v>-5.801108834351527</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6353131715763585</v>
+        <v>0.777009766631414</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.04429101024611</v>
+        <v>-0.9438861457731416</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.471235118538106</v>
+        <v>2.531478037221888</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881119554478</v>
+        <v>3.798811195544779</v>
       </c>
       <c r="C1924" t="n">
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.888749965014814</v>
+        <v>-5.534508477377175</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7231475731498951</v>
+        <v>0.8648441682049506</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.04429101024611</v>
+        <v>-0.9438861457731416</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.452429377321902</v>
+        <v>2.512672296005683</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712292</v>
+        <v>3.797691308712291</v>
       </c>
       <c r="C1925" t="n">
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.648319468209953</v>
+        <v>-5.294077980572315</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8210628484967164</v>
+        <v>0.9627594435517719</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8038605134412502</v>
+        <v>-0.7034556489682813</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.598430752029695</v>
+        <v>2.658673670713477</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837682</v>
+        <v>3.821589933837681</v>
       </c>
       <c r="C1926" t="n">
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.405528660560508</v>
+        <v>-5.051287172922869</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9221084853913148</v>
+        <v>1.06380508044637</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8038605134412502</v>
+        <v>-0.7034556489682813</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.602360065864516</v>
+        <v>2.662602984548297</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.165923568953419</v>
+        <v>-4.81168208131578</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.01862910595149</v>
+        <v>1.160325701006546</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7368125657727557</v>
+        <v>-0.6364077012997867</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.643267418382952</v>
+        <v>2.703510337066734</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.923267980530255</v>
+        <v>-4.569026492892617</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.112689412540749</v>
+        <v>1.254386007595805</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7368125657727557</v>
+        <v>-0.6364077012997867</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.640265489602946</v>
+        <v>2.700508408286727</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.703247182493245</v>
+        <v>-4.349005694855606</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.202276768766168</v>
+        <v>1.343973363821223</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5955927207047754</v>
+        <v>-0.4951878562318065</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.726576433654348</v>
+        <v>2.786819352338129</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.503998552588436</v>
+        <v>-4.149757064950797</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.297870403529915</v>
+        <v>1.43956699858497</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5955927207047754</v>
+        <v>-0.4951878562318065</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.742470616456171</v>
+        <v>2.802713535139953</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>3.100972093319338</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.344483449069066</v>
+        <v>-3.990241961431427</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.362822289377964</v>
+        <v>1.50451888443302</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4360776171854055</v>
+        <v>-0.3356727527124366</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.839325523008095</v>
+        <v>2.899568441691876</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>3.111060195880778</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.199811303969328</v>
+        <v>-3.84556981633169</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.430779249979299</v>
+        <v>1.572475845034355</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2914054720856681</v>
+        <v>-0.1910006076126992</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.936216912629377</v>
+        <v>2.996459831313159</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>3.0263998879675</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.182041845038373</v>
+        <v>-3.827800357400734</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.353226725638403</v>
+        <v>1.494923320693459</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2736360131547125</v>
+        <v>-0.1732311486817436</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.862218280074672</v>
+        <v>2.922461198758454</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>3.048800381290066</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.095242347259363</v>
+        <v>-3.741000859621725</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.410347018072573</v>
+        <v>1.552043613127628</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2736360131547125</v>
+        <v>-0.1732311486817436</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.884618773397238</v>
+        <v>2.94486169208102</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.403317884538865</v>
+        <v>3.829145432736389</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.924375501110351</v>
+        <v>3.048872782663478</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.095242347259363</v>
+        <v>-3.911387610930851</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.410347018072573</v>
+        <v>1.48396131397739</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2736360131547125</v>
+        <v>-0.3436178999908693</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.917439298096719</v>
+        <v>2.842702042668956</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240415.xlsx
+++ b/tame_output/ON/bt/strategyON_20240415.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>27.6%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.1%</t>
+          <t>-79.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118.8%</t>
+          <t>119.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>138.5%</t>
+          <t>139.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-708.7%</t>
+          <t>-722.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.3%</t>
+          <t>-58.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.8%</t>
+          <t>-75.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.6%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>754.6%</t>
+          <t>776.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-552.7%</t>
+          <t>-553.6%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-278.1%</t>
+          <t>-283.6%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.8%</t>
+          <t>-45.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-25.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>167.0%</t>
+          <t>-30.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-227.8%</t>
+          <t>-228.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.2%</t>
+          <t>-29.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>71.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-37.8%</t>
+          <t>-38.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.0%</t>
+          <t>-23.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-147.9%</t>
+          <t>-155.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-258.4%</t>
+          <t>-247.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.9%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-32.7%</t>
+          <t>-33.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-161.8%</t>
+          <t>-155.1%</t>
         </is>
       </c>
     </row>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706671</v>
+        <v>3.29873059070667</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.1008419220155682</v>
+        <v>-0.2195611368695344</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.080635569206751</v>
+        <v>3.033147883265165</v>
       </c>
       <c r="F1845" t="n">
         <v>1.738445114349024</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.09685046922037799</v>
+        <v>-0.2155696840743442</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.080056946444068</v>
+        <v>3.032569260502481</v>
       </c>
       <c r="F1846" t="n">
         <v>1.742436567144214</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.514604492767215</v>
+        <v>-0.6333237076211813</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.910882228530396</v>
+        <v>2.863394542588809</v>
       </c>
       <c r="F1847" t="n">
         <v>1.324682543597377</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.7362264263253324</v>
+        <v>-0.8549456411792988</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.822099671706071</v>
+        <v>2.774611985764484</v>
       </c>
       <c r="F1848" t="n">
         <v>1.287156409910008</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.9442304846784096</v>
+        <v>-1.062949699532376</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.743790192918765</v>
+        <v>2.696302506977179</v>
       </c>
       <c r="F1849" t="n">
         <v>1.287156409910008</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.214630447387295</v>
+        <v>-1.333349662241261</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.630711664173199</v>
+        <v>2.583223978231613</v>
       </c>
       <c r="F1850" t="n">
         <v>1.016756447201123</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.553788824975817</v>
+        <v>-1.672508039829783</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.48813261244424</v>
+        <v>2.440644926502653</v>
       </c>
       <c r="F1851" t="n">
         <v>0.6775980696126005</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.881806046703296</v>
+        <v>-2.000525261557263</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.377264013492016</v>
+        <v>2.32977632755043</v>
       </c>
       <c r="F1852" t="n">
         <v>0.3495808478851213</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.375130918238474</v>
+        <v>-2.493850133092441</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.188032815286514</v>
+        <v>2.140545129344927</v>
       </c>
       <c r="F1853" t="n">
         <v>0.2445947336455026</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.867515946262571</v>
+        <v>-2.986235161116538</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.992185196120607</v>
+        <v>1.94469751017902</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.2477902943785941</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.252696337192643</v>
+        <v>-3.37141555204661</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.836655578561441</v>
+        <v>1.789167892619855</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.2477902943785941</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.596379110419306</v>
+        <v>-3.715098325273273</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.700951592725392</v>
+        <v>1.653463906783806</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.3556963464058123</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.954029460657654</v>
+        <v>-4.072748675511621</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.553997511286311</v>
+        <v>1.506509825344724</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.7133466966441604</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.263263563653705</v>
+        <v>-4.381982778507671</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.43207679678815</v>
+        <v>1.384589110846564</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.7133466966441604</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.695069356803493</v>
+        <v>-4.813788571657459</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.245687366995639</v>
+        <v>1.198199681054053</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.8497641930854274</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.021501885671237</v>
+        <v>-5.140221100525203</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.103399130450633</v>
+        <v>1.055911444509046</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.9322324435925755</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.357164532901689</v>
+        <v>-5.475883747755655</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9677146632144167</v>
+        <v>0.9202269772728302</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.9322324435925755</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.720790777802002</v>
+        <v>-5.839509992655969</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8287517254885328</v>
+        <v>0.7812640395469463</v>
       </c>
       <c r="F1862" t="n">
         <v>-1.030454080459701</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.085918160440749</v>
+        <v>-6.204637375294715</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6819552874388655</v>
+        <v>0.634467601497279</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.326764864758714</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.494506937621427</v>
+        <v>-6.613226152475393</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.5172813205813536</v>
+        <v>0.4697936346397671</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.735353641939392</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.907489421762521</v>
+        <v>-7.026208636616487</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3472737593963764</v>
+        <v>0.2997860734547899</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.735353641939392</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.323881296049518</v>
+        <v>-7.442600510903485</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1787110602904551</v>
+        <v>0.1312233743488687</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.735353641939392</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.700558306579363</v>
+        <v>-7.819277521433329</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.03829894674719636</v>
+        <v>-0.009188739194390116</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.735353641939392</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.046433128564171</v>
+        <v>-8.165152343418137</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1039514169010318</v>
+        <v>-0.1514391028426183</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.735353641939392</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.35925792780915</v>
+        <v>-8.477977142663116</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2306764165440227</v>
+        <v>-0.2781641024856092</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.735353641939392</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.655919269619348</v>
+        <v>-8.774638484473314</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3455619773388938</v>
+        <v>-0.3930496632804803</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.804096777673271</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.089268377729583</v>
+        <v>-9.207987592583549</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5229279251173908</v>
+        <v>-0.5704156110589773</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.804096777673271</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.472269766472214</v>
+        <v>-9.590988981326181</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6762305819360273</v>
+        <v>-0.7237182678776137</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.804096777673271</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.847255092643492</v>
+        <v>-9.965974307497458</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.8236531964331082</v>
+        <v>-0.8711408823746947</v>
       </c>
       <c r="F1873" t="n">
         <v>-2.179082103844548</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.20678541514749</v>
+        <v>-10.32550463000146</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9621150221366586</v>
+        <v>-1.009602708078245</v>
       </c>
       <c r="F1874" t="n">
         <v>-2.179082103844548</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.53318544381251</v>
+        <v>-10.65190465866647</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.084759013645486</v>
+        <v>-1.132246699587073</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.505482132509561</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.7523344118867</v>
+        <v>-10.87105362674067</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.169376850253397</v>
+        <v>-1.216864536194983</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.724631100583759</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.74864348693029</v>
+        <v>-10.86736270178426</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.167900480270832</v>
+        <v>-1.215388166212418</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.724631100583759</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.95290166226016</v>
+        <v>-11.07162087711412</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.244090553284135</v>
+        <v>-1.291578239225721</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.852270045197748</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.17093943389133</v>
+        <v>-11.2896586487453</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.32682310745217</v>
+        <v>-1.374310793393757</v>
       </c>
       <c r="F1879" t="n">
         <v>-3.027040813293647</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.09746960222389</v>
+        <v>-11.21618881707785</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.282063473291769</v>
+        <v>-1.329551159233356</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.953570981626198</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.27259401961043</v>
+        <v>-11.39131323446439</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.33755801949887</v>
+        <v>-1.385045705440456</v>
       </c>
       <c r="F1881" t="n">
         <v>-3.128695399012742</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.50704611362492</v>
+        <v>-11.62576532847888</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.438558022006262</v>
+        <v>-1.486045707947848</v>
       </c>
       <c r="F1882" t="n">
         <v>-3.128695399012742</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.79484995816216</v>
+        <v>-11.91356917301612</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.560351750595134</v>
+        <v>-1.60783943653672</v>
       </c>
       <c r="F1883" t="n">
         <v>-3.41649924354998</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.02467440532598</v>
+        <v>-12.14339362017995</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.651165739622107</v>
+        <v>-1.698653425563694</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.579146780620141</v>
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.11934568980972</v>
+        <v>-12.37542253991621</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.68634052478649</v>
+        <v>-1.788771264829084</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.540754613335595</v>
+        <v>-3.641159477808564</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.037301407449791</v>
+        <v>0.9770584887660094</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.06733017584091</v>
+        <v>-12.3234070259474</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.661543983512564</v>
+        <v>-1.763974723555158</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.540754613335595</v>
+        <v>-3.641159477808564</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.041291743136191</v>
+        <v>0.9810488244524103</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.20900201756503</v>
+        <v>-12.46507886767152</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.719687947100954</v>
+        <v>-1.822118687143548</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.540754613335595</v>
+        <v>-3.641159477808564</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.03981651623745</v>
+        <v>0.9795735975536686</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.30790875802431</v>
+        <v>-12.56398560813079</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.744197233119791</v>
+        <v>-1.846627973162386</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.639661353794871</v>
+        <v>-3.740066218267839</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.9955258821267572</v>
+        <v>0.9352829634429756</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.10875665078721</v>
+        <v>-12.36483350089369</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.677587523871635</v>
+        <v>-1.780018263914229</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.474338827845057</v>
+        <v>-3.574743692318026</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.081668264049962</v>
+        <v>1.021425345366181</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.8829114980678</v>
+        <v>-12.13898834817428</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.577670389747662</v>
+        <v>-1.680101129790256</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.432412152257894</v>
+        <v>-3.532817016730863</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.116403342438469</v>
+        <v>1.056160423754688</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.5966366857451</v>
+        <v>-11.85271353585159</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.462021320262525</v>
+        <v>-1.564452060305119</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.432412152257894</v>
+        <v>-3.532817016730863</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.117542486994528</v>
+        <v>1.057299568310746</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.64953197378939</v>
+        <v>-11.90560882389588</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.480545661318132</v>
+        <v>-1.582976401360726</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.427456806169447</v>
+        <v>-3.527861670642416</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.123149468809703</v>
+        <v>1.062906550125922</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.36562324286064</v>
+        <v>-11.62170009296713</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.361248464707996</v>
+        <v>-1.46367920475059</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.427456806169447</v>
+        <v>-3.527861670642416</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.12888317304834</v>
+        <v>1.068640254364558</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.11863599266769</v>
+        <v>-11.37471284277417</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.272190827024681</v>
+        <v>-1.374621567067274</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.180469555976495</v>
+        <v>-3.280874420449464</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.267338260770245</v>
+        <v>1.207095342086464</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.85479912546362</v>
+        <v>-11.1108759755701</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.17653956145596</v>
+        <v>-1.278970301498555</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.180469555976495</v>
+        <v>-3.280874420449464</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.257454779457338</v>
+        <v>1.197211860773557</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.58755732459522</v>
+        <v>-10.84363417470171</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.071477401607975</v>
+        <v>-1.173908141650569</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.180469555976495</v>
+        <v>-3.280874420449464</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.255620218957964</v>
+        <v>1.195377300274183</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.31174816119474</v>
+        <v>-10.56782501130122</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.9614540512212417</v>
+        <v>-1.063884791263836</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.091450247697762</v>
+        <v>-3.191855112170731</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.308731488951744</v>
+        <v>1.248488570267962</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.28779462021878</v>
+        <v>-10.54387147032526</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.9512041286853647</v>
+        <v>-1.053634868727959</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.067496706721804</v>
+        <v>-3.167901571194773</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.323772119682812</v>
+        <v>1.26352920099903</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.02373468189598</v>
+        <v>-10.27981153200247</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.8588404695179985</v>
+        <v>-0.9612712095605929</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.803436768399008</v>
+        <v>-2.903841632871977</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.468947766514737</v>
+        <v>1.408704847830956</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.316655058391145</v>
+        <v>-9.57273190849763</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.5787956537763645</v>
+        <v>-0.6812263938189584</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.803436768399008</v>
+        <v>-2.903841632871977</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.466160732854436</v>
+        <v>1.405917814170655</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.276470760024955</v>
+        <v>-9.53254761013144</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.562378310542047</v>
+        <v>-0.6648090505846409</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.763252470032818</v>
+        <v>-2.863657334505787</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.490614935761992</v>
+        <v>1.430372017078211</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.19640096448715</v>
+        <v>-9.452477814593635</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5309835711061681</v>
+        <v>-0.633414311148762</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.683182674495014</v>
+        <v>-2.783587538967982</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.538023634305431</v>
+        <v>1.47778071562165</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.962919742257551</v>
+        <v>-9.218996592364036</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.4296666533764761</v>
+        <v>-0.53209739341907</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.449701452265415</v>
+        <v>-2.550106316738384</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.686036796481043</v>
+        <v>1.625793877797262</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.783211212113677</v>
+        <v>-9.039288062220162</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3606754516318857</v>
+        <v>-0.4631061916744796</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.392529948102719</v>
+        <v>-2.492934812575688</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.717447488665701</v>
+        <v>1.65720456998192</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.65093573848279</v>
+        <v>-8.907012588589275</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3123977754325038</v>
+        <v>-0.4148285154750977</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.260254474471833</v>
+        <v>-2.360659338944802</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.79218025959126</v>
+        <v>1.731937340907479</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.460336063809637</v>
+        <v>-8.716412913916121</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2333428448756059</v>
+        <v>-0.3357735849181998</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.06965479979868</v>
+        <v>-2.170059664271649</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.909355125082788</v>
+        <v>1.849112206399007</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.211336265126056</v>
+        <v>-8.46741311523254</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1208365841785146</v>
+        <v>-0.2232673242211085</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.06965479979868</v>
+        <v>-2.170059664271649</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.922261466306447</v>
+        <v>1.862018547622666</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.31692625489916</v>
+        <v>-8.573003105005645</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2910485096869753</v>
+        <v>-0.3934792497295692</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.175244789571785</v>
+        <v>-2.275649654044754</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.730931542843366</v>
+        <v>1.670688624159584</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.335661157017757</v>
+        <v>-8.591738007124242</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2499981286573276</v>
+        <v>-0.3524288686999215</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.175244789571785</v>
+        <v>-2.275649654044754</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.779475884720452</v>
+        <v>1.719232966036671</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.058922982346944</v>
+        <v>-8.314999832453429</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1359238468030077</v>
+        <v>-0.2383545868456016</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.993428128461859</v>
+        <v>-2.093832992934828</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.891944893372402</v>
+        <v>1.831701974688621</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.932030575911874</v>
+        <v>-8.188107426018359</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.09388087048245763</v>
+        <v>-0.196311610525052</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.866535722026789</v>
+        <v>-1.966940586499758</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.959366350979966</v>
+        <v>1.899123432296185</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.888482169141183</v>
+        <v>-8.144559019247668</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.08342211986927461</v>
+        <v>-0.1858528599118685</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.866535722026789</v>
+        <v>-1.966940586499758</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.952405738884873</v>
+        <v>1.892162820201092</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.646333775687325</v>
+        <v>-7.902410625793809</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.02789959189341173</v>
+        <v>-0.07453114814918216</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.866535722026789</v>
+        <v>-1.966940586499758</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.966868093266016</v>
+        <v>1.906625174582235</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.583104403918977</v>
+        <v>-7.839181254025461</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.04772346105994574</v>
+        <v>-0.05470727898264771</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.866535722026789</v>
+        <v>-1.966940586499758</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.961400213725211</v>
+        <v>1.90115729504143</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.396616711541971</v>
+        <v>-7.652693561648455</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1198166320213252</v>
+        <v>0.01738589197873175</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.680048029649783</v>
+        <v>-1.780452894122752</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.070790923161992</v>
+        <v>2.01054800447821</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389905</v>
+        <v>3.812450103389904</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.375467512638528</v>
+        <v>-7.631544362745012</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.135977289820028</v>
+        <v>0.03354654977743454</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.658898830746339</v>
+        <v>-1.759303695219308</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.091181420741383</v>
+        <v>2.030938502057602</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.74832483278809</v>
+        <v>3.748324832788089</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.131702070655083</v>
+        <v>-7.492891516980707</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2292641749604565</v>
+        <v>0.08478839643020697</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.658898830746339</v>
+        <v>-1.759303695219308</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.086962129088434</v>
+        <v>2.026719210404653</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527522</v>
+        <v>3.824307657527521</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.867674003461824</v>
+        <v>-7.228863449787447</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3369997157577762</v>
+        <v>0.1925239372275271</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.457033431930386</v>
+        <v>-1.557438296403355</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.210205682298022</v>
+        <v>2.149962763614241</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749181</v>
+        <v>3.82635139874918</v>
       </c>
       <c r="C1919" t="n">
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.617823609512749</v>
+        <v>-6.979013055838372</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4296819483211083</v>
+        <v>0.2852061697908592</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.457033431930386</v>
+        <v>-1.557438296403355</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.202947757281724</v>
+        <v>2.142704838597943</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481494</v>
+        <v>3.835954411481493</v>
       </c>
       <c r="C1920" t="n">
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.31425612050877</v>
+        <v>-6.675445566834393</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5547080674433484</v>
+        <v>0.4102322889130994</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.457033431930386</v>
+        <v>-1.557438296403355</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.206546880802373</v>
+        <v>2.146303962118592</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862983</v>
+        <v>3.780930335862982</v>
       </c>
       <c r="C1921" t="n">
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.240776211656756</v>
+        <v>-6.60196565798238</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5974275370387079</v>
+        <v>0.4529517585084588</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.383553523078371</v>
+        <v>-1.48395838755134</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.263962332168135</v>
+        <v>2.203719413484354</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102778</v>
+        <v>3.773761647102777</v>
       </c>
       <c r="C1922" t="n">
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.015743211987933</v>
+        <v>-6.376932658313557</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6864612145225339</v>
+        <v>0.5419854359922849</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.158520523409548</v>
+        <v>-1.258925387882517</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.398002609585726</v>
+        <v>2.337759690901945</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353071</v>
+        <v>3.76461430435307</v>
       </c>
       <c r="C1923" t="n">
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.801108834351527</v>
+        <v>-6.16229828067715</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.777009766631414</v>
+        <v>0.6325339881011649</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.9438861457731416</v>
+        <v>-1.04429101024611</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.531478037221888</v>
+        <v>2.471235118538106</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544779</v>
+        <v>3.798811195544778</v>
       </c>
       <c r="C1924" t="n">
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.534508477377175</v>
+        <v>-5.895697923702798</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8648441682049506</v>
+        <v>0.7203683896747011</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.9438861457731416</v>
+        <v>-1.04429101024611</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.512672296005683</v>
+        <v>2.452429377321902</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712291</v>
+        <v>3.79769130871229</v>
       </c>
       <c r="C1925" t="n">
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.294077980572315</v>
+        <v>-5.655267426897938</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9627594435517719</v>
+        <v>0.8182836650215228</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7034556489682813</v>
+        <v>-0.8038605134412502</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.658673670713477</v>
+        <v>2.598430752029695</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837681</v>
+        <v>3.82158993383768</v>
       </c>
       <c r="C1926" t="n">
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.051287172922869</v>
+        <v>-5.412476619248492</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.06380508044637</v>
+        <v>0.9193293019161213</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7034556489682813</v>
+        <v>-0.8038605134412502</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.662602984548297</v>
+        <v>2.602360065864516</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349964</v>
+        <v>3.822323422349962</v>
       </c>
       <c r="C1927" t="n">
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.81168208131578</v>
+        <v>-5.172871527641403</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.160325701006546</v>
+        <v>1.015849922476297</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.6364077012997867</v>
+        <v>-0.7368125657727557</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.703510337066734</v>
+        <v>2.643267418382952</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972337</v>
+        <v>3.848613050972335</v>
       </c>
       <c r="C1928" t="n">
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.569026492892617</v>
+        <v>-4.93021593921824</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.254386007595805</v>
+        <v>1.109910229065556</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.6364077012997867</v>
+        <v>-0.7368125657727557</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.700508408286727</v>
+        <v>2.640265489602946</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145937</v>
+        <v>3.818665376145935</v>
       </c>
       <c r="C1929" t="n">
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.349005694855606</v>
+        <v>-4.710195141181229</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.343973363821223</v>
+        <v>1.199497585290974</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4951878562318065</v>
+        <v>-0.5955927207047754</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.786819352338129</v>
+        <v>2.726576433654348</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009949</v>
+        <v>3.843270952009947</v>
       </c>
       <c r="C1930" t="n">
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.149757064950797</v>
+        <v>-4.51094651127642</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.43956699858497</v>
+        <v>1.295091220054721</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4951878562318065</v>
+        <v>-0.5955927207047754</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.802713535139953</v>
+        <v>2.742470616456171</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966256</v>
+        <v>3.845043810966255</v>
       </c>
       <c r="C1931" t="n">
         <v>3.100972093319338</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.990241961431427</v>
+        <v>-4.35143140775705</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.50451888443302</v>
+        <v>1.360043105902771</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3356727527124366</v>
+        <v>-0.4360776171854055</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.899568441691876</v>
+        <v>2.839325523008095</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046992</v>
+        <v>3.791269976046991</v>
       </c>
       <c r="C1932" t="n">
         <v>3.111060195880778</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.84556981633169</v>
+        <v>-4.206759262657313</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.572475845034355</v>
+        <v>1.428000066504106</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1910006076126992</v>
+        <v>-0.2914054720856681</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.996459831313159</v>
+        <v>2.936216912629377</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412099</v>
+        <v>3.735835647412097</v>
       </c>
       <c r="C1933" t="n">
         <v>3.0263998879675</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.827800357400734</v>
+        <v>-4.188989803726357</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.494923320693459</v>
+        <v>1.35044754216321</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1732311486817436</v>
+        <v>-0.2736360131547125</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.922461198758454</v>
+        <v>2.862218280074672</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144509</v>
+        <v>3.762643902144508</v>
       </c>
       <c r="C1934" t="n">
         <v>3.048800381290066</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.741000859621725</v>
+        <v>-3.960696163296105</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.552043613127628</v>
+        <v>1.464165491657877</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.1732311486817436</v>
+        <v>-0.2736360131547125</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.94486169208102</v>
+        <v>2.884618773397238</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.829145432736389</v>
+        <v>3.556783899872416</v>
       </c>
       <c r="C1935" t="n">
         <v>3.048872782663478</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.911387610930851</v>
+        <v>-3.920409160762412</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.48396131397739</v>
+        <v>1.480352694044766</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3436178999908693</v>
+        <v>-0.2333490106210198</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.842702042668956</v>
+        <v>2.908863376290866</v>
       </c>
     </row>
   </sheetData>
